--- a/Fruto - Pipeline - Export. KK - Fieldspec/analise_completa_resultados_cv.xlsx
+++ b/Fruto - Pipeline - Export. KK - Fieldspec/analise_completa_resultados_cv.xlsx
@@ -502,24 +502,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.5578943322551501</v>
+        <v>0.5669195341052531</v>
       </c>
       <c r="F2" t="n">
-        <v>0.315666469673087</v>
+        <v>0.3364492880678446</v>
       </c>
       <c r="G2" t="n">
-        <v>3.107677832672979</v>
+        <v>3.029541318473416</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5578943322551501</v>
+        <v>0.5669195341052531</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2.892055511474609</v>
+        <v>10.15805864334106</v>
       </c>
     </row>
     <row r="3">
@@ -530,7 +530,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -544,24 +544,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.4926810748000555</v>
+        <v>0.5589771181434884</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3154044796110611</v>
+        <v>0.2386015091660678</v>
       </c>
       <c r="G3" t="n">
-        <v>3.355226480894292</v>
+        <v>3.31719731770179</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4926810748000555</v>
+        <v>0.5589771181434884</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__C': 100, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>8.326411962509155</v>
+        <v>176.8239214420319</v>
       </c>
     </row>
     <row r="4">
@@ -577,25 +577,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>OSC_1</t>
+          <t>Continuum_Removal</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4900387036016897</v>
+        <v>0.4925496548044211</v>
       </c>
       <c r="F4" t="n">
-        <v>0.406060131211479</v>
+        <v>0.3157042156317443</v>
       </c>
       <c r="G4" t="n">
-        <v>3.377457622021752</v>
+        <v>3.355401233689391</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4900387036016897</v>
+        <v>0.4925496548044211</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1.248669385910034</v>
+        <v>6.664275646209717</v>
       </c>
     </row>
     <row r="5">
@@ -619,25 +619,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SNV</t>
+          <t>OSC_1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4891027413802865</v>
+        <v>0.4898224616546315</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5281783240979918</v>
+        <v>0.4064893288835792</v>
       </c>
       <c r="G5" t="n">
-        <v>3.217519151795958</v>
+        <v>3.377640799981552</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4891027413802865</v>
+        <v>0.4898224616546315</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.8818485736846924</v>
+        <v>0.7909166812896729</v>
       </c>
     </row>
     <row r="6">
@@ -656,12 +656,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Continuum_Removal</t>
+          <t>SNV</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -670,24 +670,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.4764970111925325</v>
+        <v>0.4892149854011975</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2343014609120195</v>
+        <v>0.5280252680251405</v>
       </c>
       <c r="G6" t="n">
-        <v>3.705144602126632</v>
+        <v>3.217244840156141</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4764970111925325</v>
+        <v>0.4892149854011975</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>50.1351363658905</v>
+        <v>0.5911629199981689</v>
       </c>
     </row>
     <row r="7">
@@ -703,7 +703,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OSC_1</t>
+          <t>OSC_2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -712,24 +712,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.4567186436338374</v>
+        <v>0.4682053338927871</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3115969290443156</v>
+        <v>0.3113732304793524</v>
       </c>
       <c r="G7" t="n">
-        <v>3.803209282313144</v>
+        <v>3.572813117073518</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4567186436338374</v>
+        <v>0.4682053338927871</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2.067941188812256</v>
+        <v>7.034550666809082</v>
       </c>
     </row>
     <row r="8">
@@ -745,33 +745,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>OSC_1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.4478479719677903</v>
+        <v>0.4670841160445794</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3811606497051964</v>
+        <v>0.2827041370560262</v>
       </c>
       <c r="G8" t="n">
-        <v>3.710250075919141</v>
+        <v>3.808118046148805</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4478479719677903</v>
+        <v>0.4670841160445794</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+          <t>{'model__C': 10, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1.985568523406982</v>
+        <v>5.624130249023438</v>
       </c>
     </row>
     <row r="9">
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SNV_Detrend_SG_D1</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2.045872688293457</v>
+        <v>4.234918117523193</v>
       </c>
     </row>
     <row r="10">
@@ -829,25 +829,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wavelet_Denoising</t>
+          <t>SNV_Detrend_SG_D1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.4475528305323097</v>
+        <v>0.4478479719677903</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3823462856088357</v>
+        <v>0.3811606497051964</v>
       </c>
       <c r="G10" t="n">
-        <v>3.710059283811896</v>
+        <v>3.710250075919141</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4475528305323097</v>
+        <v>0.4478479719677903</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2.863781452178955</v>
+        <v>4.030038118362427</v>
       </c>
     </row>
     <row r="11">
@@ -866,12 +866,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>Wavelet_Denoising</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -880,24 +880,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.4402636502683322</v>
+        <v>0.4475528305323097</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5356985180887979</v>
+        <v>0.3823462856088357</v>
       </c>
       <c r="G11" t="n">
-        <v>3.341617861579523</v>
+        <v>3.710059283811896</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4402636502683322</v>
+        <v>0.4475528305323097</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.9408349990844727</v>
+        <v>9.691274404525757</v>
       </c>
     </row>
     <row r="12">
@@ -908,38 +908,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MSC_SG_OSC</t>
+          <t>EMSC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.4398891658607645</v>
+        <v>0.4415069915198419</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4462151248473926</v>
+        <v>0.5338762143193495</v>
       </c>
       <c r="G12" t="n">
-        <v>3.468692825972729</v>
+        <v>3.34106221448199</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4398891658607645</v>
+        <v>0.4415069915198419</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'model__n_components': 5}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1.114665269851685</v>
+        <v>0.713209867477417</v>
       </c>
     </row>
     <row r="13">
@@ -950,38 +950,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>OSC_2</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.4398414529759546</v>
+        <v>0.4400651810818003</v>
       </c>
       <c r="F13" t="n">
-        <v>0.303446523910984</v>
+        <v>0.5357383062337698</v>
       </c>
       <c r="G13" t="n">
-        <v>3.857051627116417</v>
+        <v>3.342595540008369</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4398414529759546</v>
+        <v>0.4400651810818003</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2.37683367729187</v>
+        <v>0.6639161109924316</v>
       </c>
     </row>
     <row r="14">
@@ -992,38 +992,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EMSC</t>
+          <t>MSC_SG_OSC</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.439116490421512</v>
+        <v>0.4398891658607645</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5373690427135663</v>
+        <v>0.4462151248473926</v>
       </c>
       <c r="G14" t="n">
-        <v>3.343289727768511</v>
+        <v>3.468692825972729</v>
       </c>
       <c r="H14" t="n">
-        <v>0.439116490421512</v>
+        <v>0.4398891658607645</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__n_components': 5}</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.8570234775543213</v>
+        <v>0.8905603885650635</v>
       </c>
     </row>
     <row r="15">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.8683738708496094</v>
+        <v>0.6918418407440186</v>
       </c>
     </row>
     <row r="16">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0.8288278579711914</v>
+        <v>0.5850486755371094</v>
       </c>
     </row>
     <row r="17">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0.9185636043548584</v>
+        <v>0.7404639720916748</v>
       </c>
     </row>
     <row r="18">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1.047940731048584</v>
+        <v>0.5553925037384033</v>
       </c>
     </row>
     <row r="19">
@@ -1216,16 +1216,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.4223206980391261</v>
+        <v>0.4223372055080065</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5097565743111276</v>
+        <v>0.5096484102874739</v>
       </c>
       <c r="G19" t="n">
-        <v>3.538147590368146</v>
+        <v>3.538018582708018</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4223206980391261</v>
+        <v>0.4223372055080065</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1.755676507949829</v>
+        <v>0.8206112384796143</v>
       </c>
     </row>
     <row r="20">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.995563268661499</v>
+        <v>0.5875067710876465</v>
       </c>
     </row>
     <row r="21">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1300,24 +1300,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.4134712966346078</v>
+        <v>0.4204124551679305</v>
       </c>
       <c r="F21" t="n">
-        <v>0.563257571286066</v>
+        <v>0.4189734929486491</v>
       </c>
       <c r="G21" t="n">
-        <v>3.39889825101891</v>
+        <v>3.787090645443048</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4134712966346078</v>
+        <v>0.4204124551679305</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__C': 10, 'model__epsilon': 1.0, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0.8078238964080811</v>
+        <v>3.627764225006104</v>
       </c>
     </row>
     <row r="22">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Detrend</t>
+          <t>SG_D1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1342,24 +1342,24 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.4029823198902239</v>
+        <v>0.414721659439146</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4383400225609791</v>
+        <v>0.1482866386997891</v>
       </c>
       <c r="G22" t="n">
-        <v>3.823294073627603</v>
+        <v>4.150772506581068</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4029823198902239</v>
+        <v>0.414721659439146</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1.963712215423584</v>
+        <v>4.188417434692383</v>
       </c>
     </row>
     <row r="23">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Normalize</t>
+          <t>Detrend</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1384,16 +1384,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.4012752695828902</v>
+        <v>0.4133237768454849</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6074574564047155</v>
+        <v>0.5632571954764315</v>
       </c>
       <c r="G23" t="n">
-        <v>3.380572268015235</v>
+        <v>3.398762491958384</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4012752695828902</v>
+        <v>0.4133237768454849</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0.7650196552276611</v>
+        <v>0.5851428508758545</v>
       </c>
     </row>
     <row r="24">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Detrend</t>
+          <t>Normalize</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1426,24 +1426,24 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.3923102233790249</v>
+        <v>0.4013896555162487</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4487069673083148</v>
+        <v>0.6071597830201106</v>
       </c>
       <c r="G24" t="n">
-        <v>3.66666556084102</v>
+        <v>3.380761717098151</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3923102233790249</v>
+        <v>0.4013896555162487</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'model__n_components': 10}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0.9687490463256836</v>
+        <v>0.5987391471862793</v>
       </c>
     </row>
     <row r="25">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Detrend</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1468,16 +1468,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.3911759102530376</v>
+        <v>0.3923102233790249</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4302752123046786</v>
+        <v>0.4487069673083148</v>
       </c>
       <c r="G25" t="n">
-        <v>3.724218280137297</v>
+        <v>3.66666556084102</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3911759102530376</v>
+        <v>0.3923102233790249</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1.121502161026001</v>
+        <v>0.5593297481536865</v>
       </c>
     </row>
     <row r="26">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SNV_Detrend_SG_D1</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0.7531993389129639</v>
+        <v>0.5481405258178711</v>
       </c>
     </row>
     <row r="27">
@@ -1543,25 +1543,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wavelet_Denoising</t>
+          <t>SNV_Detrend_SG_D1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.3911422584163475</v>
+        <v>0.3911759102530376</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4299260599715061</v>
+        <v>0.4302752123046786</v>
       </c>
       <c r="G27" t="n">
-        <v>3.724492596988249</v>
+        <v>3.724218280137297</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3911422584163475</v>
+        <v>0.3911759102530376</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>1.051527976989746</v>
+        <v>0.5501842498779297</v>
       </c>
     </row>
     <row r="28">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Wavelet_Denoising</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1594,24 +1594,24 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.3896658214896413</v>
+        <v>0.3911422584163475</v>
       </c>
       <c r="F28" t="n">
-        <v>0.533336400568624</v>
+        <v>0.4299260599715061</v>
       </c>
       <c r="G28" t="n">
-        <v>3.553423317335124</v>
+        <v>3.724492596988249</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3896658214896413</v>
+        <v>0.3911422584163475</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__n_components': 10}</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0.7997298240661621</v>
+        <v>0.6947190761566162</v>
       </c>
     </row>
     <row r="29">
@@ -1636,16 +1636,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.3896393488608526</v>
+        <v>0.3896834640118904</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5334609771116255</v>
+        <v>0.533515499328477</v>
       </c>
       <c r="G29" t="n">
-        <v>3.553767587659209</v>
+        <v>3.553846930358251</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3896393488608526</v>
+        <v>0.3896834640118904</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0.8471450805664062</v>
+        <v>0.7085671424865723</v>
       </c>
     </row>
     <row r="30">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wavelet_Denoising</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1678,16 +1678,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.3886744717346095</v>
+        <v>0.389669107454104</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5336674364045008</v>
+        <v>0.5334315530535355</v>
       </c>
       <c r="G30" t="n">
-        <v>3.557376798834814</v>
+        <v>3.554046273429765</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3886744717346095</v>
+        <v>0.389669107454104</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>1.106439828872681</v>
+        <v>0.5860753059387207</v>
       </c>
     </row>
     <row r="31">
@@ -1711,33 +1711,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MSC_SG_OSC</t>
+          <t>Wavelet_Denoising</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.3860856816308583</v>
+        <v>0.3885761961509223</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4713366705728805</v>
+        <v>0.5338510801609341</v>
       </c>
       <c r="G31" t="n">
-        <v>3.807518571739907</v>
+        <v>3.557214826643528</v>
       </c>
       <c r="H31" t="n">
-        <v>0.3860856816308583</v>
+        <v>0.3885761961509223</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 10}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>1.34232234954834</v>
+        <v>0.8981184959411621</v>
       </c>
     </row>
     <row r="32">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OPLS1_SNV_SG_D1</t>
+          <t>MSC_SG_OSC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1762,16 +1762,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.3851189109057406</v>
+        <v>0.3861001285303524</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4851497478414317</v>
+        <v>0.4713467091377089</v>
       </c>
       <c r="G32" t="n">
-        <v>3.783915626968373</v>
+        <v>3.807488156505627</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3851189109057406</v>
+        <v>0.3861001285303524</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>1.016900062561035</v>
+        <v>1.042800426483154</v>
       </c>
     </row>
     <row r="33">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MSC_SG_OSC</t>
+          <t>OPLS1_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1804,24 +1804,24 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.3734314816823642</v>
+        <v>0.3851180182963658</v>
       </c>
       <c r="F33" t="n">
-        <v>0.33632850563486</v>
+        <v>0.485131354941977</v>
       </c>
       <c r="G33" t="n">
-        <v>4.11002741172179</v>
+        <v>3.783964237767703</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3734314816823642</v>
+        <v>0.3851180182963658</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__pca__n_components': 10}</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>4.093920469284058</v>
+        <v>0.8617000579833984</v>
       </c>
     </row>
     <row r="34">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OPLS1_SNV_SG_D1</t>
+          <t>MSC_SG_OSC</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1846,24 +1846,24 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.3716683081856272</v>
+        <v>0.3814773807901722</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3334969928739742</v>
+        <v>0.3650921585236366</v>
       </c>
       <c r="G34" t="n">
-        <v>4.107625426350892</v>
+        <v>3.723093907221457</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3716683081856272</v>
+        <v>0.3814773807901722</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>2.523782730102539</v>
+        <v>13.6131911277771</v>
       </c>
     </row>
     <row r="35">
@@ -1874,38 +1874,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SG_D1</t>
+          <t>OPLS1_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.3692456383951021</v>
+        <v>0.3775285353886996</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5013549010828731</v>
+        <v>0.3739738386086923</v>
       </c>
       <c r="G35" t="n">
-        <v>3.806645242951868</v>
+        <v>3.724511404885646</v>
       </c>
       <c r="H35" t="n">
-        <v>0.3692456383951021</v>
+        <v>0.3775285353886996</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 10}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0.8292279243469238</v>
+        <v>8.358203411102295</v>
       </c>
     </row>
     <row r="36">
@@ -1916,38 +1916,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OPLS2_SNV_SG_D1</t>
+          <t>SNV</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.3674910458999786</v>
+        <v>0.3749044578986849</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4396188678506294</v>
+        <v>0.5226093271797104</v>
       </c>
       <c r="G36" t="n">
-        <v>3.705067664842105</v>
+        <v>3.69457413250132</v>
       </c>
       <c r="H36" t="n">
-        <v>0.3674910458999786</v>
+        <v>0.3749044578986849</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>1.142669677734375</v>
+        <v>4.841625213623047</v>
       </c>
     </row>
     <row r="37">
@@ -1958,38 +1958,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>OSC_1</t>
+          <t>SG_D1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.3612302744902333</v>
+        <v>0.3692371105505016</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4774902289866049</v>
+        <v>0.5014164740180551</v>
       </c>
       <c r="G37" t="n">
-        <v>3.722897319227577</v>
+        <v>3.806440718044457</v>
       </c>
       <c r="H37" t="n">
-        <v>0.3612302744902333</v>
+        <v>0.3692371105505016</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>{'model__n_components': 10}</t>
+          <t>{'model__pca__n_components': 10}</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0.885368824005127</v>
+        <v>0.580087423324585</v>
       </c>
     </row>
     <row r="38">
@@ -2000,38 +2000,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>OPLS2_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.3240432632975108</v>
+        <v>0.3678941890435575</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5609241887329375</v>
+        <v>0.4399367903329463</v>
       </c>
       <c r="G38" t="n">
-        <v>4.217026473043804</v>
+        <v>3.70430884570458</v>
       </c>
       <c r="H38" t="n">
-        <v>0.3240432632975108</v>
+        <v>0.3678941890435575</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>2.620939493179321</v>
+        <v>0.9990959167480469</v>
       </c>
     </row>
     <row r="39">
@@ -2042,38 +2042,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EMSC</t>
+          <t>OSC_1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.324043263297509</v>
+        <v>0.3612302744902333</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5609241887329433</v>
+        <v>0.4774902289866049</v>
       </c>
       <c r="G39" t="n">
-        <v>4.217026473043811</v>
+        <v>3.722897319227577</v>
       </c>
       <c r="H39" t="n">
-        <v>0.324043263297509</v>
+        <v>0.3612302744902333</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__n_components': 10}</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>2.214208364486694</v>
+        <v>0.6087822914123535</v>
       </c>
     </row>
     <row r="40">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SNV</t>
+          <t>EMSC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2098,24 +2098,24 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.3156946404325982</v>
+        <v>0.3317060870897939</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5210199741268717</v>
+        <v>0.7427501975500673</v>
       </c>
       <c r="G40" t="n">
-        <v>4.307795777300062</v>
+        <v>3.62581416054391</v>
       </c>
       <c r="H40" t="n">
-        <v>0.3156946404325982</v>
+        <v>0.3317060870897939</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 0.01, 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>2.008397102355957</v>
+        <v>5.041629076004028</v>
       </c>
     </row>
     <row r="41">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Normalize</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2140,24 +2140,24 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.3046735982931046</v>
+        <v>0.3317060870681326</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5698890166576264</v>
+        <v>0.7427501976720258</v>
       </c>
       <c r="G41" t="n">
-        <v>4.243589293752868</v>
+        <v>3.625814160568009</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3046735982931046</v>
+        <v>0.3317060870681326</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>1.994377851486206</v>
+        <v>7.745988607406616</v>
       </c>
     </row>
     <row r="42">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SNV</t>
+          <t>Normalize</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2182,24 +2182,24 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.3034684497993924</v>
+        <v>0.3182749163805302</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5115451003337432</v>
+        <v>0.5731451596278331</v>
       </c>
       <c r="G42" t="n">
-        <v>3.887768177598764</v>
+        <v>4.180717022339208</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3034684497993924</v>
+        <v>0.3182749163805302</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>{'model__n_components': 10}</t>
+          <t>{'model__C': 10, 'model__epsilon': 1.0, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>0.9469966888427734</v>
+        <v>3.798267602920532</v>
       </c>
     </row>
     <row r="43">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>EMSC</t>
+          <t>SNV</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2224,24 +2224,24 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.2938496033615136</v>
+        <v>0.3034684497993924</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4765449133516282</v>
+        <v>0.5115451003337432</v>
       </c>
       <c r="G43" t="n">
-        <v>4.544392449426272</v>
+        <v>3.887768177598764</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2938496033615136</v>
+        <v>0.3034684497993924</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>{'model__n_components': 5}</t>
+          <t>{'model__n_components': 10}</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>1.021985769271851</v>
+        <v>0.5570545196533203</v>
       </c>
     </row>
     <row r="44">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>EMSC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2266,16 +2266,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.2938496033614506</v>
+        <v>0.2938496033615136</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4765449133517757</v>
+        <v>0.4765449133516282</v>
       </c>
       <c r="G44" t="n">
-        <v>4.544392449426566</v>
+        <v>4.544392449426272</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2938496033614506</v>
+        <v>0.2938496033615136</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>1.108165502548218</v>
+        <v>0.5880904197692871</v>
       </c>
     </row>
     <row r="45">
@@ -2299,33 +2299,33 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>OSC_2</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.2826866255409842</v>
+        <v>0.2938496033614506</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5472021609567463</v>
+        <v>0.4765449133517757</v>
       </c>
       <c r="G45" t="n">
-        <v>3.948913753875976</v>
+        <v>4.544392449426566</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2826866255409842</v>
+        <v>0.2938496033614506</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>{'model__n_components': 10}</t>
+          <t>{'model__n_components': 5}</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>0.8570940494537354</v>
+        <v>0.61163330078125</v>
       </c>
     </row>
     <row r="46">
@@ -2341,33 +2341,33 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Continuum_Removal</t>
+          <t>OSC_2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.2719659233526829</v>
+        <v>0.2826866255409842</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4892793546262471</v>
+        <v>0.5472021609567463</v>
       </c>
       <c r="G46" t="n">
-        <v>4.084878840195476</v>
+        <v>3.948913753875976</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2719659233526829</v>
+        <v>0.2826866255409842</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>{'model__n_components': 5}</t>
+          <t>{'model__n_components': 10}</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>8.331249952316284</v>
+        <v>0.6387929916381836</v>
       </c>
     </row>
     <row r="47">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SG_D2</t>
+          <t>Continuum_Removal</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2392,24 +2392,24 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.03483528336387358</v>
+        <v>0.2719659233526829</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2998874739118955</v>
+        <v>0.4892793546262471</v>
       </c>
       <c r="G47" t="n">
-        <v>5.373890736795365</v>
+        <v>4.084878840195476</v>
       </c>
       <c r="H47" t="n">
-        <v>0.03483528336387358</v>
+        <v>0.2719659233526829</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__n_components': 5}</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>2.245530366897583</v>
+        <v>6.289379596710205</v>
       </c>
     </row>
     <row r="48">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2434,24 +2434,24 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-0.06512600850415078</v>
+        <v>0.05644915984791064</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7120115228908238</v>
+        <v>0.2520224150530852</v>
       </c>
       <c r="G48" t="n">
-        <v>5.223827623259522</v>
+        <v>5.285267824863806</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.06512600850415078</v>
+        <v>0.05644915984791064</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 15}</t>
+          <t>{'model__C': 10, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>0.8325400352478027</v>
+        <v>4.148954629898071</v>
       </c>
     </row>
     <row r="49">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SG_D1</t>
+          <t>SG_D2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2476,24 +2476,24 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-0.06575793946323476</v>
+        <v>-0.06327387668202956</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3519019085297117</v>
+        <v>0.7108655734523039</v>
       </c>
       <c r="G49" t="n">
-        <v>5.850143806976877</v>
+        <v>5.221575834166602</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.06575793946323476</v>
+        <v>-0.06327387668202956</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__pca__n_components': 15}</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>2.581528186798096</v>
+        <v>0.8434104919433594</v>
       </c>
     </row>
     <row r="50">
@@ -2518,16 +2518,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.4005945527011846</v>
+        <v>0.4008241796943971</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2350186864765451</v>
+        <v>0.2349487154254113</v>
       </c>
       <c r="G50" t="n">
-        <v>1.083561380858318</v>
+        <v>1.083707743578178</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4005945527011846</v>
+        <v>0.4008241796943971</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>1.210336208343506</v>
+        <v>0.6341357231140137</v>
       </c>
     </row>
     <row r="51">
@@ -2560,24 +2560,24 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.3691817704195285</v>
+        <v>0.3927625814690664</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2616689298424897</v>
+        <v>0.2615866448468673</v>
       </c>
       <c r="G51" t="n">
-        <v>1.140695957192287</v>
+        <v>1.120120095267253</v>
       </c>
       <c r="H51" t="n">
-        <v>0.3691817704195285</v>
+        <v>0.3927625814690664</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 0.01, 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>2.245423316955566</v>
+        <v>4.533736228942871</v>
       </c>
     </row>
     <row r="52">
@@ -2588,38 +2588,38 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MSC_SG_OSC</t>
+          <t>Normalize</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.3447574644102044</v>
+        <v>0.3922628279971108</v>
       </c>
       <c r="F52" t="n">
-        <v>0.3565150100744908</v>
+        <v>0.2277967018595562</v>
       </c>
       <c r="G52" t="n">
-        <v>1.077738139263447</v>
+        <v>1.091330471052878</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3447574644102044</v>
+        <v>0.3922628279971108</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 15}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>1.358602285385132</v>
+        <v>3.793725252151489</v>
       </c>
     </row>
     <row r="53">
@@ -2630,38 +2630,38 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OPLS1_SNV_SG_D1</t>
+          <t>EMSC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.343931263222835</v>
+        <v>0.3892833508384059</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3555354094962101</v>
+        <v>0.1632208923932641</v>
       </c>
       <c r="G53" t="n">
-        <v>1.077446902469166</v>
+        <v>1.129224969878984</v>
       </c>
       <c r="H53" t="n">
-        <v>0.343931263222835</v>
+        <v>0.3892833508384059</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 15}</t>
+          <t>{'model__C': 10, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>1.17850661277771</v>
+        <v>5.15120530128479</v>
       </c>
     </row>
     <row r="54">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>EMSC</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2686,24 +2686,24 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.3055465113762269</v>
+        <v>0.3892833508361929</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2856181386931465</v>
+        <v>0.1632208923941465</v>
       </c>
       <c r="G54" t="n">
-        <v>1.151185583059109</v>
+        <v>1.129224969877927</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3055465113762269</v>
+        <v>0.3892833508361929</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 10, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>2.258668184280396</v>
+        <v>7.029271841049194</v>
       </c>
     </row>
     <row r="55">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>SG_D1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2728,24 +2728,24 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.3055465113761945</v>
+        <v>0.3857348503161226</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2856181386931483</v>
+        <v>0.1743876040942624</v>
       </c>
       <c r="G55" t="n">
-        <v>1.151185583059141</v>
+        <v>1.093367035088294</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3055465113761945</v>
+        <v>0.3857348503161226</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>3.875827789306641</v>
+        <v>3.904603958129883</v>
       </c>
     </row>
     <row r="56">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OPLS2_SNV_SG_D1</t>
+          <t>OSC_1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2770,24 +2770,24 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.3048035769120582</v>
+        <v>0.3685444010219938</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3609125538718836</v>
+        <v>0.1696985466512033</v>
       </c>
       <c r="G56" t="n">
-        <v>1.118256099579986</v>
+        <v>1.159168360804733</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3048035769120582</v>
+        <v>0.3685444010219938</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 15}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>1.304891109466553</v>
+        <v>7.369142293930054</v>
       </c>
     </row>
     <row r="57">
@@ -2798,38 +2798,38 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OSC_1</t>
+          <t>Detrend</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.2761957479670219</v>
+        <v>0.3477847543825464</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2117595545392677</v>
+        <v>0.15853513511706</v>
       </c>
       <c r="G57" t="n">
-        <v>1.242004695642706</v>
+        <v>1.175333325468552</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2761957479670219</v>
+        <v>0.3477847543825464</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 10}</t>
+          <t>{'model__C': 10, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1.048515558242798</v>
+        <v>3.936015605926514</v>
       </c>
     </row>
     <row r="58">
@@ -2845,33 +2845,33 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>EMSC</t>
+          <t>MSC_SG_OSC</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.2674050144990474</v>
+        <v>0.3447749716905926</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3469704344718199</v>
+        <v>0.3565416732208969</v>
       </c>
       <c r="G58" t="n">
-        <v>1.27563246063669</v>
+        <v>1.077880814202642</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2674050144990474</v>
+        <v>0.3447749716905926</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__pca__n_components': 15}</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>1.271452903747559</v>
+        <v>1.07972264289856</v>
       </c>
     </row>
     <row r="59">
@@ -2887,33 +2887,33 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>OPLS1_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.2670628054263863</v>
+        <v>0.3443517667090382</v>
       </c>
       <c r="F59" t="n">
-        <v>0.3472523572827698</v>
+        <v>0.3545827483215953</v>
       </c>
       <c r="G59" t="n">
-        <v>1.275548316345246</v>
+        <v>1.077262526941389</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2670628054263863</v>
+        <v>0.3443517667090382</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__pca__n_components': 15}</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>1.414039373397827</v>
+        <v>0.780200719833374</v>
       </c>
     </row>
     <row r="60">
@@ -2929,33 +2929,33 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>OSC_2</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.258195706500569</v>
+        <v>0.3261703506351112</v>
       </c>
       <c r="F60" t="n">
-        <v>0.362104118025378</v>
+        <v>0.1832603714746841</v>
       </c>
       <c r="G60" t="n">
-        <v>1.225179221009538</v>
+        <v>1.205269443806168</v>
       </c>
       <c r="H60" t="n">
-        <v>0.258195706500569</v>
+        <v>0.3261703506351112</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>{'model__C': 1, 'model__epsilon': 0.1, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>3.113706350326538</v>
+        <v>4.187660932540894</v>
       </c>
     </row>
     <row r="61">
@@ -2966,38 +2966,38 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Detrend</t>
+          <t>SNV_Detrend_SG_D1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.2540062795860737</v>
+        <v>0.3261703506351112</v>
       </c>
       <c r="F61" t="n">
-        <v>0.3831906702551616</v>
+        <v>0.1832603714746841</v>
       </c>
       <c r="G61" t="n">
-        <v>1.270792970562428</v>
+        <v>1.205269443806168</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2540062795860737</v>
+        <v>0.3261703506351112</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>1.098652601242065</v>
+        <v>4.528153419494629</v>
       </c>
     </row>
     <row r="62">
@@ -3008,38 +3008,38 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OSC_2</t>
+          <t>Wavelet_Denoising</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.2442384001195321</v>
+        <v>0.3183950156767795</v>
       </c>
       <c r="F62" t="n">
-        <v>0.379837380622513</v>
+        <v>0.1882854593989846</v>
       </c>
       <c r="G62" t="n">
-        <v>1.325104497021059</v>
+        <v>1.209054866199619</v>
       </c>
       <c r="H62" t="n">
-        <v>0.2442384001195321</v>
+        <v>0.3183950156767795</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 15}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>1.15748929977417</v>
+        <v>10.4328887462616</v>
       </c>
     </row>
     <row r="63">
@@ -3055,33 +3055,33 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SNV</t>
+          <t>OPLS2_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.2334977212474103</v>
+        <v>0.3047830684747346</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2160850070473408</v>
+        <v>0.3610282518556135</v>
       </c>
       <c r="G63" t="n">
-        <v>1.269784318690338</v>
+        <v>1.118243513337384</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2334977212474103</v>
+        <v>0.3047830684747346</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 10}</t>
+          <t>{'model__pca__n_components': 15}</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>1.19618034362793</v>
+        <v>0.7709252834320068</v>
       </c>
     </row>
     <row r="64">
@@ -3092,38 +3092,38 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>OSC_1</t>
+          <t>Continuum_Removal</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.229122349261583</v>
+        <v>0.2905375623150367</v>
       </c>
       <c r="F64" t="n">
-        <v>0.2514536045705735</v>
+        <v>0.3514845955897322</v>
       </c>
       <c r="G64" t="n">
-        <v>1.270274805731018</v>
+        <v>1.135388909606466</v>
       </c>
       <c r="H64" t="n">
-        <v>0.229122349261583</v>
+        <v>0.2905375623150367</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>{'model__n_components': 5}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>1.245585441589355</v>
+        <v>177.8681190013885</v>
       </c>
     </row>
     <row r="65">
@@ -3134,38 +3134,38 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Normalize</t>
+          <t>OSC_2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.2275611080808192</v>
+        <v>0.2837905662064443</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2679346806276658</v>
+        <v>0.3076348768966038</v>
       </c>
       <c r="G65" t="n">
-        <v>1.243429538095805</v>
+        <v>1.21724762055812</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2275611080808192</v>
+        <v>0.2837905662064443</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 10}</t>
+          <t>{'model__C': 1, 'model__epsilon': 1.0, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>1.339387178421021</v>
+        <v>7.803299188613892</v>
       </c>
     </row>
     <row r="66">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OPLS2_SNV_SG_D1</t>
+          <t>MSC_SG_OSC</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3190,24 +3190,24 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.2254174917112269</v>
+        <v>0.2821772647762465</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4901613909062962</v>
+        <v>0.4474286270358056</v>
       </c>
       <c r="G66" t="n">
-        <v>1.160417767802103</v>
+        <v>1.102279028317463</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2254174917112269</v>
+        <v>0.2821772647762465</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>{'model__C': 1, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>3.936188697814941</v>
+        <v>15.03517532348633</v>
       </c>
     </row>
     <row r="67">
@@ -3223,33 +3223,33 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wavelet_Denoising</t>
+          <t>OSC_1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.2198170730684382</v>
+        <v>0.2761979176513553</v>
       </c>
       <c r="F67" t="n">
-        <v>0.239636484562759</v>
+        <v>0.2117576821205483</v>
       </c>
       <c r="G67" t="n">
-        <v>1.307998321348268</v>
+        <v>1.242003730864933</v>
       </c>
       <c r="H67" t="n">
-        <v>0.2198170730684382</v>
+        <v>0.2761979176513553</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 15}</t>
+          <t>{'model__pca__n_components': 10}</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>1.241359233856201</v>
+        <v>0.8541650772094727</v>
       </c>
     </row>
     <row r="68">
@@ -3260,38 +3260,38 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>OPLS1_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.2188781247783576</v>
+        <v>0.2743273750254208</v>
       </c>
       <c r="F68" t="n">
-        <v>0.2401928165726981</v>
+        <v>0.4682595670741278</v>
       </c>
       <c r="G68" t="n">
-        <v>1.308360982727829</v>
+        <v>1.100987947040668</v>
       </c>
       <c r="H68" t="n">
-        <v>0.2188781247783576</v>
+        <v>0.2743273750254208</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 15}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>1.233388662338257</v>
+        <v>9.149951457977295</v>
       </c>
     </row>
     <row r="69">
@@ -3307,33 +3307,33 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SNV_Detrend_SG_D1</t>
+          <t>EMSC</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.2188598690433906</v>
+        <v>0.2675885965694722</v>
       </c>
       <c r="F69" t="n">
-        <v>0.2401915856760981</v>
+        <v>0.3473945437591035</v>
       </c>
       <c r="G69" t="n">
-        <v>1.308372760908225</v>
+        <v>1.275504022429116</v>
       </c>
       <c r="H69" t="n">
-        <v>0.2188598690433906</v>
+        <v>0.2675885965694722</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 15}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>1.285286664962769</v>
+        <v>0.8693740367889404</v>
       </c>
     </row>
     <row r="70">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3358,24 +3358,24 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.218453622867736</v>
+        <v>0.2673737993831031</v>
       </c>
       <c r="F70" t="n">
-        <v>0.4745232785819427</v>
+        <v>0.3471533477249161</v>
       </c>
       <c r="G70" t="n">
-        <v>1.185262727049401</v>
+        <v>1.275227802603337</v>
       </c>
       <c r="H70" t="n">
-        <v>0.218453622867736</v>
+        <v>0.2673737993831031</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>1.959012985229492</v>
+        <v>0.8027439117431641</v>
       </c>
     </row>
     <row r="71">
@@ -3386,38 +3386,38 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SNV_Detrend_SG_D1</t>
+          <t>Detrend</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.218453622867736</v>
+        <v>0.2539779524882921</v>
       </c>
       <c r="F71" t="n">
-        <v>0.4745232785819427</v>
+        <v>0.3833593544276724</v>
       </c>
       <c r="G71" t="n">
-        <v>1.185262727049401</v>
+        <v>1.270988761928902</v>
       </c>
       <c r="H71" t="n">
-        <v>0.218453622867736</v>
+        <v>0.2539779524882921</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>2.095522880554199</v>
+        <v>0.6104552745819092</v>
       </c>
     </row>
     <row r="72">
@@ -3428,38 +3428,38 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wavelet_Denoising</t>
+          <t>OSC_2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.2184272996350822</v>
+        <v>0.2442931247979844</v>
       </c>
       <c r="F72" t="n">
-        <v>0.4746573400472076</v>
+        <v>0.3798030209981159</v>
       </c>
       <c r="G72" t="n">
-        <v>1.185264205238027</v>
+        <v>1.325134554829982</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2184272996350822</v>
+        <v>0.2442931247979844</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__pca__n_components': 15}</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>4.306098699569702</v>
+        <v>0.974257230758667</v>
       </c>
     </row>
     <row r="73">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OSC_1</t>
+          <t>OPLS2_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3484,24 +3484,24 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.2153099325243835</v>
+        <v>0.2364292109106874</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4557048382663758</v>
+        <v>0.517560837631978</v>
       </c>
       <c r="G73" t="n">
-        <v>1.240199971921325</v>
+        <v>1.14720200064811</v>
       </c>
       <c r="H73" t="n">
-        <v>0.2153099325243835</v>
+        <v>0.2364292109106874</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+          <t>{'model__C': 10, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>2.657076358795166</v>
+        <v>10.28945755958557</v>
       </c>
     </row>
     <row r="74">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Continuum_Removal</t>
+          <t>SNV</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3526,24 +3526,24 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.2111643281168318</v>
+        <v>0.2334975879760799</v>
       </c>
       <c r="F74" t="n">
-        <v>0.5475509524819749</v>
+        <v>0.2160843747818395</v>
       </c>
       <c r="G74" t="n">
-        <v>1.204188766490474</v>
+        <v>1.2697829904917</v>
       </c>
       <c r="H74" t="n">
-        <v>0.2111643281168318</v>
+        <v>0.2334975879760799</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>{'model__n_components': 5}</t>
+          <t>{'model__pca__n_components': 10}</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>10.21876049041748</v>
+        <v>0.6329333782196045</v>
       </c>
     </row>
     <row r="75">
@@ -3554,38 +3554,38 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Continuum_Removal</t>
+          <t>OSC_1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.2035251785424227</v>
+        <v>0.229122349261583</v>
       </c>
       <c r="F75" t="n">
-        <v>0.4557737413402495</v>
+        <v>0.2514536045705735</v>
       </c>
       <c r="G75" t="n">
-        <v>1.263230407759199</v>
+        <v>1.270274805731018</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2035251785424227</v>
+        <v>0.229122349261583</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__n_components': 5}</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>9.405636310577393</v>
+        <v>0.7176277637481689</v>
       </c>
     </row>
     <row r="76">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SNV</t>
+          <t>Normalize</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3610,24 +3610,24 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.2015898573387683</v>
+        <v>0.2275622313906959</v>
       </c>
       <c r="F76" t="n">
-        <v>0.4033542193728632</v>
+        <v>0.2679328549018776</v>
       </c>
       <c r="G76" t="n">
-        <v>1.241297873825084</v>
+        <v>1.243429721558633</v>
       </c>
       <c r="H76" t="n">
-        <v>0.2015898573387683</v>
+        <v>0.2275622313906959</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>{'model__n_components': 5}</t>
+          <t>{'model__pca__n_components': 10}</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>1.132714986801147</v>
+        <v>0.8518736362457275</v>
       </c>
     </row>
     <row r="77">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Continuum_Removal</t>
+          <t>Wavelet_Denoising</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3652,24 +3652,24 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.1994287887943642</v>
+        <v>0.2197998478487415</v>
       </c>
       <c r="F77" t="n">
-        <v>0.3545673780766094</v>
+        <v>0.2396075163619602</v>
       </c>
       <c r="G77" t="n">
-        <v>1.233253284699696</v>
+        <v>1.308012447718792</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1994287887943642</v>
+        <v>0.2197998478487415</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+          <t>{'model__pca__n_components': 15}</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>52.83371520042419</v>
+        <v>0.9721972942352295</v>
       </c>
     </row>
     <row r="78">
@@ -3680,38 +3680,38 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Detrend</t>
+          <t>SNV_Detrend_SG_D1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.1833473274935024</v>
+        <v>0.2188903178083876</v>
       </c>
       <c r="F78" t="n">
-        <v>0.4574442264133163</v>
+        <v>0.2402079541623416</v>
       </c>
       <c r="G78" t="n">
-        <v>1.24711841834723</v>
+        <v>1.308372674808909</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1833473274935024</v>
+        <v>0.2188903178083876</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+          <t>{'model__pca__n_components': 15}</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>2.062109470367432</v>
+        <v>0.6015279293060303</v>
       </c>
     </row>
     <row r="79">
@@ -3722,38 +3722,38 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OSC_2</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.1806626340268321</v>
+        <v>0.2188677676421222</v>
       </c>
       <c r="F79" t="n">
-        <v>0.3657011774054099</v>
+        <v>0.2402144506767823</v>
       </c>
       <c r="G79" t="n">
-        <v>1.318469901274105</v>
+        <v>1.308369615920979</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1806626340268321</v>
+        <v>0.2188677676421222</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>{'model__n_components': 5}</t>
+          <t>{'model__pca__n_components': 15}</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>1.477428197860718</v>
+        <v>0.7404129505157471</v>
       </c>
     </row>
     <row r="80">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Normalize</t>
+          <t>Continuum_Removal</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3778,24 +3778,24 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.1777648804227772</v>
+        <v>0.2111643281168318</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3129809289175263</v>
+        <v>0.5475509524819749</v>
       </c>
       <c r="G80" t="n">
-        <v>1.281989605304861</v>
+        <v>1.204188766490474</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1777648804227772</v>
+        <v>0.2111643281168318</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>{'model__C': 1, 'model__epsilon': 0.5, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__n_components': 5}</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>1.940036535263062</v>
+        <v>6.51332688331604</v>
       </c>
     </row>
     <row r="81">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Detrend</t>
+          <t>Continuum_Removal</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3820,24 +3820,24 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.1651452471030189</v>
+        <v>0.2039166040901728</v>
       </c>
       <c r="F81" t="n">
-        <v>0.441575122916269</v>
+        <v>0.4547215240307087</v>
       </c>
       <c r="G81" t="n">
-        <v>1.252986873231444</v>
+        <v>1.263504465523502</v>
       </c>
       <c r="H81" t="n">
-        <v>0.1651452471030189</v>
+        <v>0.2039166040901728</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>{'model__n_components': 5}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>1.095342636108398</v>
+        <v>7.081070423126221</v>
       </c>
     </row>
     <row r="82">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SG_D2</t>
+          <t>SNV</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3862,16 +3862,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.1380802044513791</v>
+        <v>0.2015898573387683</v>
       </c>
       <c r="F82" t="n">
-        <v>0.409868109294612</v>
+        <v>0.4033542193728632</v>
       </c>
       <c r="G82" t="n">
-        <v>1.220940239883517</v>
+        <v>1.241297873825084</v>
       </c>
       <c r="H82" t="n">
-        <v>0.1380802044513791</v>
+        <v>0.2015898573387683</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>1.264523506164551</v>
+        <v>0.6600320339202881</v>
       </c>
     </row>
     <row r="83">
@@ -3890,38 +3890,38 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SG_D1</t>
+          <t>OSC_2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.1215256487019437</v>
+        <v>0.1806626340268321</v>
       </c>
       <c r="F83" t="n">
-        <v>0.2878268747521021</v>
+        <v>0.3657011774054099</v>
       </c>
       <c r="G83" t="n">
-        <v>1.311787043495019</v>
+        <v>1.318469901274105</v>
       </c>
       <c r="H83" t="n">
-        <v>0.1215256487019437</v>
+        <v>0.1806626340268321</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__n_components': 5}</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>2.247388601303101</v>
+        <v>0.7150089740753174</v>
       </c>
     </row>
     <row r="84">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wavelet_Denoising</t>
+          <t>Detrend</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3946,16 +3946,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.1201465663767144</v>
+        <v>0.1651452471030189</v>
       </c>
       <c r="F84" t="n">
-        <v>0.5809116622838628</v>
+        <v>0.441575122916269</v>
       </c>
       <c r="G84" t="n">
-        <v>1.2638645203059</v>
+        <v>1.252986873231444</v>
       </c>
       <c r="H84" t="n">
-        <v>0.1201465663767144</v>
+        <v>0.1651452471030189</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>1.528645038604736</v>
+        <v>0.8162214756011963</v>
       </c>
     </row>
     <row r="85">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>SG_D2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3988,16 +3988,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.1201439878507112</v>
+        <v>0.1380802044513791</v>
       </c>
       <c r="F85" t="n">
-        <v>0.5807682684890363</v>
+        <v>0.409868109294612</v>
       </c>
       <c r="G85" t="n">
-        <v>1.263875805879368</v>
+        <v>1.220940239883517</v>
       </c>
       <c r="H85" t="n">
-        <v>0.1201439878507112</v>
+        <v>0.1380802044513791</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>1.117088079452515</v>
+        <v>0.7217175960540771</v>
       </c>
     </row>
     <row r="86">
@@ -4021,25 +4021,25 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SNV_Detrend_SG_D1</t>
+          <t>Wavelet_Denoising</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.1201439878507112</v>
+        <v>0.1201465663767144</v>
       </c>
       <c r="F86" t="n">
-        <v>0.5807682684890363</v>
+        <v>0.5809116622838628</v>
       </c>
       <c r="G86" t="n">
-        <v>1.263875805879368</v>
+        <v>1.2638645203059</v>
       </c>
       <c r="H86" t="n">
-        <v>0.1201439878507112</v>
+        <v>0.1201465663767144</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>1.190607786178589</v>
+        <v>0.7850048542022705</v>
       </c>
     </row>
     <row r="87">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Normalize</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4072,16 +4072,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.08935885662512841</v>
+        <v>0.1201439878507112</v>
       </c>
       <c r="F87" t="n">
-        <v>0.46694747916403</v>
+        <v>0.5807682684890363</v>
       </c>
       <c r="G87" t="n">
-        <v>1.301991305996351</v>
+        <v>1.263875805879368</v>
       </c>
       <c r="H87" t="n">
-        <v>0.08935885662512841</v>
+        <v>0.1201439878507112</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>1.321799516677856</v>
+        <v>0.6737194061279297</v>
       </c>
     </row>
     <row r="88">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MSC_SG_OSC</t>
+          <t>SNV_Detrend_SG_D1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4114,24 +4114,24 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.08275481663048694</v>
+        <v>0.1201439878507112</v>
       </c>
       <c r="F88" t="n">
-        <v>0.4697802903915698</v>
+        <v>0.5807682684890363</v>
       </c>
       <c r="G88" t="n">
-        <v>1.259941393552428</v>
+        <v>1.263875805879368</v>
       </c>
       <c r="H88" t="n">
-        <v>0.08275481663048694</v>
+        <v>0.1201439878507112</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__n_components': 5}</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>5.105334520339966</v>
+        <v>0.6868300437927246</v>
       </c>
     </row>
     <row r="89">
@@ -4147,33 +4147,33 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>OPLS1_SNV_SG_D1</t>
+          <t>SG_D2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.0736504820785062</v>
+        <v>0.09682722140780302</v>
       </c>
       <c r="F89" t="n">
-        <v>0.5059037208510213</v>
+        <v>0.5406149669686097</v>
       </c>
       <c r="G89" t="n">
-        <v>1.256958551920069</v>
+        <v>1.227695687247545</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0736504820785062</v>
+        <v>0.09682722140780302</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>3.245229721069336</v>
+        <v>3.885562181472778</v>
       </c>
     </row>
     <row r="90">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SG_D1</t>
+          <t>Normalize</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4198,16 +4198,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.07349607599478761</v>
+        <v>0.08935885662512841</v>
       </c>
       <c r="F90" t="n">
-        <v>0.677230718239016</v>
+        <v>0.46694747916403</v>
       </c>
       <c r="G90" t="n">
-        <v>1.280047946202789</v>
+        <v>1.301991305996351</v>
       </c>
       <c r="H90" t="n">
-        <v>0.07349607599478761</v>
+        <v>0.08935885662512841</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>1.273159980773926</v>
+        <v>0.6605405807495117</v>
       </c>
     </row>
     <row r="91">
@@ -4231,25 +4231,25 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MSC_SG_OSC</t>
+          <t>SG_D1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.04939844733922481</v>
+        <v>0.07349607599478761</v>
       </c>
       <c r="F91" t="n">
-        <v>0.4980306258460142</v>
+        <v>0.677230718239016</v>
       </c>
       <c r="G91" t="n">
-        <v>1.323326808566762</v>
+        <v>1.280047946202789</v>
       </c>
       <c r="H91" t="n">
-        <v>0.04939844733922481</v>
+        <v>0.07349607599478761</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>1.63892650604248</v>
+        <v>0.6384701728820801</v>
       </c>
     </row>
     <row r="92">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>OPLS1_SNV_SG_D1</t>
+          <t>MSC_SG_OSC</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4282,16 +4282,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.02580579753582006</v>
+        <v>0.04939844733922481</v>
       </c>
       <c r="F92" t="n">
-        <v>0.524266794038964</v>
+        <v>0.4980306258460142</v>
       </c>
       <c r="G92" t="n">
-        <v>1.340344326139833</v>
+        <v>1.323326808566762</v>
       </c>
       <c r="H92" t="n">
-        <v>0.02580579753582006</v>
+        <v>0.04939844733922481</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>1.327756881713867</v>
+        <v>0.9299676418304443</v>
       </c>
     </row>
     <row r="93">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>OPLS2_SNV_SG_D1</t>
+          <t>OPLS1_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4324,16 +4324,16 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.01267081083527208</v>
+        <v>0.02580579753582006</v>
       </c>
       <c r="F93" t="n">
-        <v>0.5215345417943376</v>
+        <v>0.524266794038964</v>
       </c>
       <c r="G93" t="n">
-        <v>1.369623540184786</v>
+        <v>1.340344326139833</v>
       </c>
       <c r="H93" t="n">
-        <v>0.01267081083527208</v>
+        <v>0.02580579753582006</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>1.427933931350708</v>
+        <v>0.7896273136138916</v>
       </c>
     </row>
     <row r="94">
@@ -4352,38 +4352,38 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SG_D2</t>
+          <t>OPLS2_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>-0.03032161875296007</v>
+        <v>0.01267081083527208</v>
       </c>
       <c r="F94" t="n">
-        <v>0.4986316419591504</v>
+        <v>0.5215345417943376</v>
       </c>
       <c r="G94" t="n">
-        <v>1.3267267531961</v>
+        <v>1.369623540184786</v>
       </c>
       <c r="H94" t="n">
-        <v>-0.03032161875296007</v>
+        <v>0.01267081083527208</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 15}</t>
+          <t>{'model__n_components': 5}</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>1.196612358093262</v>
+        <v>0.8938055038452148</v>
       </c>
     </row>
     <row r="95">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>EMSC</t>
+          <t>SG_D2</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4408,24 +4408,24 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>-0.03259726149316648</v>
+        <v>-0.03090519199737209</v>
       </c>
       <c r="F95" t="n">
-        <v>0.4386247965676232</v>
+        <v>0.4992745891425146</v>
       </c>
       <c r="G95" t="n">
-        <v>1.416792300152976</v>
+        <v>1.326762514852212</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.03259726149316648</v>
+        <v>-0.03090519199737209</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>{'model__n_components': 5}</t>
+          <t>{'model__pca__n_components': 15}</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>1.225538969039917</v>
+        <v>0.6247861385345459</v>
       </c>
     </row>
     <row r="96">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>EMSC</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4450,16 +4450,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>-0.03259726149349401</v>
+        <v>-0.03259726149316648</v>
       </c>
       <c r="F96" t="n">
-        <v>0.4386247965679326</v>
+        <v>0.4386247965676232</v>
       </c>
       <c r="G96" t="n">
-        <v>1.416792300153161</v>
+        <v>1.416792300152976</v>
       </c>
       <c r="H96" t="n">
-        <v>-0.03259726149349401</v>
+        <v>-0.03259726149316648</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>1.366392374038696</v>
+        <v>0.6944756507873535</v>
       </c>
     </row>
     <row r="97">
@@ -4478,12 +4478,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SG_D2</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4492,24 +4492,24 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>-0.04573228769791415</v>
+        <v>-0.03259726149349401</v>
       </c>
       <c r="F97" t="n">
-        <v>0.2595063060170917</v>
+        <v>0.4386247965679326</v>
       </c>
       <c r="G97" t="n">
-        <v>1.435287828977491</v>
+        <v>1.416792300153161</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.04573228769791415</v>
+        <v>-0.03259726149349401</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>{'model__C': 1, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__n_components': 5}</t>
         </is>
       </c>
       <c r="J97" t="n">
-        <v>2.397594928741455</v>
+        <v>0.7470977306365967</v>
       </c>
     </row>
     <row r="98">
@@ -4520,38 +4520,38 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>OSC_2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9114811022922005</v>
+        <v>0.9259378636635663</v>
       </c>
       <c r="F98" t="n">
-        <v>0.07429386253431151</v>
+        <v>0.02518883950903613</v>
       </c>
       <c r="G98" t="n">
-        <v>13.72133498402767</v>
+        <v>12.65721757964652</v>
       </c>
       <c r="H98" t="n">
-        <v>0.9114811022922005</v>
+        <v>0.9259378636635663</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>0.9189262390136719</v>
+        <v>7.985027074813843</v>
       </c>
     </row>
     <row r="99">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>EMSC</t>
+          <t>SNV</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4576,24 +4576,24 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9114578717392643</v>
+        <v>0.9139438396013453</v>
       </c>
       <c r="F99" t="n">
-        <v>0.07435180132102891</v>
+        <v>0.06882366949021677</v>
       </c>
       <c r="G99" t="n">
-        <v>13.72233572848632</v>
+        <v>13.35012507972007</v>
       </c>
       <c r="H99" t="n">
-        <v>0.9114578717392643</v>
+        <v>0.9139438396013453</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__C': 100, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>0.8417561054229736</v>
+        <v>3.970992088317871</v>
       </c>
     </row>
     <row r="100">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Detrend</t>
+          <t>EMSC</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4618,24 +4618,24 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9107751123160485</v>
+        <v>0.9114507446111777</v>
       </c>
       <c r="F100" t="n">
-        <v>0.05058511270154382</v>
+        <v>0.07436754900132202</v>
       </c>
       <c r="G100" t="n">
-        <v>13.4859426210611</v>
+        <v>13.71856741058486</v>
       </c>
       <c r="H100" t="n">
-        <v>0.9107751123160485</v>
+        <v>0.9114507446111777</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>{'model__n_components': 15}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>0.7250573635101318</v>
+        <v>0.6437621116638184</v>
       </c>
     </row>
     <row r="101">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Normalize</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4660,24 +4660,24 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9103987974625026</v>
+        <v>0.9114268723926078</v>
       </c>
       <c r="F101" t="n">
-        <v>0.05734270413334482</v>
+        <v>0.07431291585589599</v>
       </c>
       <c r="G101" t="n">
-        <v>13.84079127881909</v>
+        <v>13.72181363920459</v>
       </c>
       <c r="H101" t="n">
-        <v>0.9103987974625026</v>
+        <v>0.9114268723926078</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>{'model__n_components': 10}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J101" t="n">
-        <v>0.6631085872650146</v>
+        <v>0.5790503025054932</v>
       </c>
     </row>
     <row r="102">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SNV</t>
+          <t>Detrend</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4702,16 +4702,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9101851987321412</v>
+        <v>0.9107751123160485</v>
       </c>
       <c r="F102" t="n">
-        <v>0.06641443314731242</v>
+        <v>0.05058511270154382</v>
       </c>
       <c r="G102" t="n">
-        <v>13.91340204657388</v>
+        <v>13.4859426210611</v>
       </c>
       <c r="H102" t="n">
-        <v>0.9101851987321412</v>
+        <v>0.9107751123160485</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>0.6899735927581787</v>
+        <v>0.5337646007537842</v>
       </c>
     </row>
     <row r="103">
@@ -4735,33 +4735,33 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>OSC_1</t>
+          <t>Normalize</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9101178001281267</v>
+        <v>0.9103987974625026</v>
       </c>
       <c r="F103" t="n">
-        <v>0.06374692477042727</v>
+        <v>0.05734270413334482</v>
       </c>
       <c r="G103" t="n">
-        <v>13.878610886004</v>
+        <v>13.84079127881909</v>
       </c>
       <c r="H103" t="n">
-        <v>0.9101178001281267</v>
+        <v>0.9103987974625026</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>{'model__n_components': 15}</t>
+          <t>{'model__n_components': 10}</t>
         </is>
       </c>
       <c r="J103" t="n">
-        <v>0.833716869354248</v>
+        <v>0.5214135646820068</v>
       </c>
     </row>
     <row r="104">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>SNV</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4786,16 +4786,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9080434632139063</v>
+        <v>0.9101851987321412</v>
       </c>
       <c r="F104" t="n">
-        <v>0.07623050723927596</v>
+        <v>0.06641443314731242</v>
       </c>
       <c r="G104" t="n">
-        <v>13.95900769922678</v>
+        <v>13.91340204657388</v>
       </c>
       <c r="H104" t="n">
-        <v>0.9080434632139063</v>
+        <v>0.9101851987321412</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>3.787834167480469</v>
+        <v>0.5485899448394775</v>
       </c>
     </row>
     <row r="105">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SNV_Detrend_SG_D1</t>
+          <t>OSC_1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4828,16 +4828,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9080434632139063</v>
+        <v>0.9101178001281267</v>
       </c>
       <c r="F105" t="n">
-        <v>0.07623050723927596</v>
+        <v>0.06374692477042727</v>
       </c>
       <c r="G105" t="n">
-        <v>13.95900769922678</v>
+        <v>13.878610886004</v>
       </c>
       <c r="H105" t="n">
-        <v>0.9080434632139063</v>
+        <v>0.9101178001281267</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>0.7606964111328125</v>
+        <v>0.5595307350158691</v>
       </c>
     </row>
     <row r="106">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Detrend</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4870,24 +4870,24 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9069514849689394</v>
+        <v>0.9080434632139063</v>
       </c>
       <c r="F106" t="n">
-        <v>0.08079630252105588</v>
+        <v>0.07623050723927596</v>
       </c>
       <c r="G106" t="n">
-        <v>13.98265525535864</v>
+        <v>13.95900769922678</v>
       </c>
       <c r="H106" t="n">
-        <v>0.9069514849689394</v>
+        <v>0.9080434632139063</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__n_components': 15}</t>
         </is>
       </c>
       <c r="J106" t="n">
-        <v>0.7669045925140381</v>
+        <v>2.492214918136597</v>
       </c>
     </row>
     <row r="107">
@@ -4903,25 +4903,25 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wavelet_Denoising</t>
+          <t>SNV_Detrend_SG_D1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9068985811232529</v>
+        <v>0.9080434632139063</v>
       </c>
       <c r="F107" t="n">
-        <v>0.07711973698161866</v>
+        <v>0.07623050723927596</v>
       </c>
       <c r="G107" t="n">
-        <v>14.04359078534846</v>
+        <v>13.95900769922678</v>
       </c>
       <c r="H107" t="n">
-        <v>0.9068985811232529</v>
+        <v>0.9080434632139063</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>0.9727015495300293</v>
+        <v>0.5144202709197998</v>
       </c>
     </row>
     <row r="108">
@@ -4940,38 +4940,38 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>OPLS1_SNV_SG_D1</t>
+          <t>Wavelet_Denoising</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9056544938356911</v>
+        <v>0.9068985811232529</v>
       </c>
       <c r="F108" t="n">
-        <v>0.06291611281967965</v>
+        <v>0.07711973698161866</v>
       </c>
       <c r="G108" t="n">
-        <v>13.93479851447273</v>
+        <v>14.04359078534846</v>
       </c>
       <c r="H108" t="n">
-        <v>0.9056544938356911</v>
+        <v>0.9068985811232529</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__n_components': 15}</t>
         </is>
       </c>
       <c r="J108" t="n">
-        <v>0.8679711818695068</v>
+        <v>0.6163113117218018</v>
       </c>
     </row>
     <row r="109">
@@ -4982,38 +4982,38 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>OPLS1_SNV_SG_D1</t>
+          <t>Detrend</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.904085026727957</v>
+        <v>0.9068889412274069</v>
       </c>
       <c r="F109" t="n">
-        <v>0.05676992374391144</v>
+        <v>0.0807763257521829</v>
       </c>
       <c r="G109" t="n">
-        <v>14.14692682686671</v>
+        <v>13.97903764010328</v>
       </c>
       <c r="H109" t="n">
-        <v>0.904085026727957</v>
+        <v>0.9068889412274069</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>{'model__n_components': 5}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J109" t="n">
-        <v>0.9535977840423584</v>
+        <v>0.6077389717102051</v>
       </c>
     </row>
     <row r="110">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MSC_SG_OSC</t>
+          <t>OPLS1_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5038,24 +5038,24 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9035254411756177</v>
+        <v>0.9057569677209468</v>
       </c>
       <c r="F110" t="n">
-        <v>0.05635363658155412</v>
+        <v>0.06293863009076735</v>
       </c>
       <c r="G110" t="n">
-        <v>14.19114187159586</v>
+        <v>13.93400583164189</v>
       </c>
       <c r="H110" t="n">
-        <v>0.9035254411756177</v>
+        <v>0.9057569677209468</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>{'model__n_components': 5}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J110" t="n">
-        <v>1.143747091293335</v>
+        <v>0.7224187850952148</v>
       </c>
     </row>
     <row r="111">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MSC_SG_OSC</t>
+          <t>OPLS1_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5080,24 +5080,24 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.903128362379132</v>
+        <v>0.904085026727957</v>
       </c>
       <c r="F111" t="n">
-        <v>0.06177844058807554</v>
+        <v>0.05676992374391144</v>
       </c>
       <c r="G111" t="n">
-        <v>14.15739407484952</v>
+        <v>14.14692682686671</v>
       </c>
       <c r="H111" t="n">
-        <v>0.903128362379132</v>
+        <v>0.904085026727957</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__n_components': 5}</t>
         </is>
       </c>
       <c r="J111" t="n">
-        <v>0.9905078411102295</v>
+        <v>0.6524157524108887</v>
       </c>
     </row>
     <row r="112">
@@ -5113,7 +5113,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>OSC_2</t>
+          <t>MSC_SG_OSC</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5122,24 +5122,24 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9031174088372674</v>
+        <v>0.9035254411756177</v>
       </c>
       <c r="F112" t="n">
-        <v>0.07180597845260248</v>
+        <v>0.05635363658155412</v>
       </c>
       <c r="G112" t="n">
-        <v>14.61142070882108</v>
+        <v>14.19114187159586</v>
       </c>
       <c r="H112" t="n">
-        <v>0.9031174088372674</v>
+        <v>0.9035254411756177</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>{'model__n_components': 10}</t>
+          <t>{'model__n_components': 5}</t>
         </is>
       </c>
       <c r="J112" t="n">
-        <v>0.9359924793243408</v>
+        <v>0.6993818283081055</v>
       </c>
     </row>
     <row r="113">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>OSC_2</t>
+          <t>MSC_SG_OSC</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5164,16 +5164,16 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.903006279089924</v>
+        <v>0.9031549382530055</v>
       </c>
       <c r="F113" t="n">
-        <v>0.06691455584494521</v>
+        <v>0.06178710437438625</v>
       </c>
       <c r="G113" t="n">
-        <v>14.14570105050608</v>
+        <v>14.15949856309902</v>
       </c>
       <c r="H113" t="n">
-        <v>0.903006279089924</v>
+        <v>0.9031549382530055</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>0.7249629497528076</v>
+        <v>0.8689274787902832</v>
       </c>
     </row>
     <row r="114">
@@ -5197,33 +5197,33 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SG_D2</t>
+          <t>OSC_2</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9028644822573865</v>
+        <v>0.9031174088372674</v>
       </c>
       <c r="F114" t="n">
-        <v>0.03999454730447156</v>
+        <v>0.07180597845260248</v>
       </c>
       <c r="G114" t="n">
-        <v>14.10012187712156</v>
+        <v>14.61142070882108</v>
       </c>
       <c r="H114" t="n">
-        <v>0.9028644822573865</v>
+        <v>0.9031174088372674</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>{'model__n_components': 5}</t>
+          <t>{'model__n_components': 10}</t>
         </is>
       </c>
       <c r="J114" t="n">
-        <v>0.7005174160003662</v>
+        <v>0.5843322277069092</v>
       </c>
     </row>
     <row r="115">
@@ -5234,38 +5234,38 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SG_D1</t>
+          <t>OSC_2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9015223460623322</v>
+        <v>0.9030265522154902</v>
       </c>
       <c r="F115" t="n">
-        <v>0.04791057157334052</v>
+        <v>0.06689711175139007</v>
       </c>
       <c r="G115" t="n">
-        <v>14.41902105370939</v>
+        <v>14.14677896839659</v>
       </c>
       <c r="H115" t="n">
-        <v>0.9015223460623322</v>
+        <v>0.9030265522154902</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>{'model__n_components': 10}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J115" t="n">
-        <v>0.856891393661499</v>
+        <v>0.663334846496582</v>
       </c>
     </row>
     <row r="116">
@@ -5276,12 +5276,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Continuum_Removal</t>
+          <t>SG_D2</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5290,24 +5290,24 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9012352717103628</v>
+        <v>0.9028644822573865</v>
       </c>
       <c r="F116" t="n">
-        <v>0.04520761654377753</v>
+        <v>0.03999454730447156</v>
       </c>
       <c r="G116" t="n">
-        <v>14.64488124331304</v>
+        <v>14.10012187712156</v>
       </c>
       <c r="H116" t="n">
-        <v>0.9012352717103628</v>
+        <v>0.9028644822573865</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__n_components': 5}</t>
         </is>
       </c>
       <c r="J116" t="n">
-        <v>7.680854320526123</v>
+        <v>0.5252771377563477</v>
       </c>
     </row>
     <row r="117">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5332,24 +5332,24 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.8955817396113186</v>
+        <v>0.9015223460623322</v>
       </c>
       <c r="F117" t="n">
-        <v>0.08346061326573354</v>
+        <v>0.04791057157334052</v>
       </c>
       <c r="G117" t="n">
-        <v>14.11534629440252</v>
+        <v>14.41902105370939</v>
       </c>
       <c r="H117" t="n">
-        <v>0.8955817396113186</v>
+        <v>0.9015223460623322</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 10}</t>
+          <t>{'model__n_components': 10}</t>
         </is>
       </c>
       <c r="J117" t="n">
-        <v>0.6881229877471924</v>
+        <v>0.5000512599945068</v>
       </c>
     </row>
     <row r="118">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5374,24 +5374,24 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.8929012578607292</v>
+        <v>0.9011918712344047</v>
       </c>
       <c r="F118" t="n">
-        <v>0.04912550907472999</v>
+        <v>0.04519898778965197</v>
       </c>
       <c r="G118" t="n">
-        <v>14.69227470571448</v>
+        <v>14.64802571920287</v>
       </c>
       <c r="H118" t="n">
-        <v>0.8929012578607292</v>
+        <v>0.9011918712344047</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>{'model__n_components': 20}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J118" t="n">
-        <v>8.668860197067261</v>
+        <v>6.143286943435669</v>
       </c>
     </row>
     <row r="119">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Normalize</t>
+          <t>SG_D1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5416,24 +5416,24 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.8909139408518254</v>
+        <v>0.8955946378825409</v>
       </c>
       <c r="F119" t="n">
-        <v>0.07950496498880365</v>
+        <v>0.08345227069554885</v>
       </c>
       <c r="G119" t="n">
-        <v>15.06683990372165</v>
+        <v>14.11530747833822</v>
       </c>
       <c r="H119" t="n">
-        <v>0.8909139408518254</v>
+        <v>0.8955946378825409</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__pca__n_components': 10}</t>
         </is>
       </c>
       <c r="J119" t="n">
-        <v>0.8156023025512695</v>
+        <v>0.5361447334289551</v>
       </c>
     </row>
     <row r="120">
@@ -5444,38 +5444,38 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>OPLS2_SNV_SG_D1</t>
+          <t>Continuum_Removal</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.887707214599005</v>
+        <v>0.8929012578607292</v>
       </c>
       <c r="F120" t="n">
-        <v>0.0900396051195318</v>
+        <v>0.04912550907472999</v>
       </c>
       <c r="G120" t="n">
-        <v>15.47368807021046</v>
+        <v>14.69227470571448</v>
       </c>
       <c r="H120" t="n">
-        <v>0.887707214599005</v>
+        <v>0.8929012578607292</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__n_components': 20}</t>
         </is>
       </c>
       <c r="J120" t="n">
-        <v>0.9510905742645264</v>
+        <v>4.240493297576904</v>
       </c>
     </row>
     <row r="121">
@@ -5486,38 +5486,38 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>OPLS2_SNV_SG_D1</t>
+          <t>Normalize</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.8874753705713948</v>
+        <v>0.8908244103936651</v>
       </c>
       <c r="F121" t="n">
-        <v>0.1055394128644625</v>
+        <v>0.07957521615221462</v>
       </c>
       <c r="G121" t="n">
-        <v>15.72842100480595</v>
+        <v>15.06723281963625</v>
       </c>
       <c r="H121" t="n">
-        <v>0.8874753705713948</v>
+        <v>0.8908244103936651</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>{'model__n_components': 10}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J121" t="n">
-        <v>0.968921422958374</v>
+        <v>0.6130485534667969</v>
       </c>
     </row>
     <row r="122">
@@ -5533,25 +5533,25 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SNV</t>
+          <t>OPLS2_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.8793589989075175</v>
+        <v>0.8876132463123497</v>
       </c>
       <c r="F122" t="n">
-        <v>0.07580787047859672</v>
+        <v>0.09019736361381375</v>
       </c>
       <c r="G122" t="n">
-        <v>15.92731881243171</v>
+        <v>15.47364341280802</v>
       </c>
       <c r="H122" t="n">
-        <v>0.8793589989075175</v>
+        <v>0.8876132463123497</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="J122" t="n">
-        <v>0.8941738605499268</v>
+        <v>0.778038501739502</v>
       </c>
     </row>
     <row r="123">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>OSC_2</t>
+          <t>OPLS2_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -5584,24 +5584,24 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.8784024345896867</v>
+        <v>0.8874753705713948</v>
       </c>
       <c r="F123" t="n">
-        <v>0.05519367468743359</v>
+        <v>0.1055394128644625</v>
       </c>
       <c r="G123" t="n">
-        <v>16.43114054643597</v>
+        <v>15.72842100480595</v>
       </c>
       <c r="H123" t="n">
-        <v>0.8784024345896867</v>
+        <v>0.8874753705713948</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__n_components': 10}</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>3.005647897720337</v>
+        <v>0.70058274269104</v>
       </c>
     </row>
     <row r="124">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>OSC_1</t>
+          <t>OPLS2_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5626,24 +5626,24 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.8713042928361189</v>
+        <v>0.8867030608340505</v>
       </c>
       <c r="F124" t="n">
-        <v>0.07979795043688961</v>
+        <v>0.1011992024383693</v>
       </c>
       <c r="G124" t="n">
-        <v>16.35306054919363</v>
+        <v>15.77434797730688</v>
       </c>
       <c r="H124" t="n">
-        <v>0.8713042928361189</v>
+        <v>0.8867030608340505</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__C': 100, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J124" t="n">
-        <v>0.6642305850982666</v>
+        <v>10.7375636100769</v>
       </c>
     </row>
     <row r="125">
@@ -5659,33 +5659,33 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SNV_Detrend_SG_D1</t>
+          <t>SNV</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.8657370085513824</v>
+        <v>0.8792517893221493</v>
       </c>
       <c r="F125" t="n">
-        <v>0.05352021023463033</v>
+        <v>0.0759867741095465</v>
       </c>
       <c r="G125" t="n">
-        <v>16.48272773478709</v>
+        <v>15.92761727444849</v>
       </c>
       <c r="H125" t="n">
-        <v>0.8657370085513824</v>
+        <v>0.8792517893221493</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 10}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J125" t="n">
-        <v>0.7805356979370117</v>
+        <v>0.5535590648651123</v>
       </c>
     </row>
     <row r="126">
@@ -5696,38 +5696,38 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>OSC_1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.8657370002647002</v>
+        <v>0.8737845286571279</v>
       </c>
       <c r="F126" t="n">
-        <v>0.05352020664344022</v>
+        <v>0.07621753828668475</v>
       </c>
       <c r="G126" t="n">
-        <v>16.48272826423184</v>
+        <v>16.65988346050072</v>
       </c>
       <c r="H126" t="n">
-        <v>0.8657370002647002</v>
+        <v>0.8737845286571279</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 10}</t>
+          <t>{'model__C': 100, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J126" t="n">
-        <v>0.7965936660766602</v>
+        <v>5.568463325500488</v>
       </c>
     </row>
     <row r="127">
@@ -5743,33 +5743,33 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Wavelet_Denoising</t>
+          <t>OSC_1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.8657358081427173</v>
+        <v>0.8713633947083244</v>
       </c>
       <c r="F127" t="n">
-        <v>0.05349654698206205</v>
+        <v>0.0797930962939552</v>
       </c>
       <c r="G127" t="n">
-        <v>16.48292988176662</v>
+        <v>16.3534013101843</v>
       </c>
       <c r="H127" t="n">
-        <v>0.8657358081427173</v>
+        <v>0.8713633947083244</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 10}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J127" t="n">
-        <v>0.8603141307830811</v>
+        <v>0.6336667537689209</v>
       </c>
     </row>
     <row r="128">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SNV</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5794,24 +5794,24 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.8388582046439572</v>
+        <v>0.8676930505169788</v>
       </c>
       <c r="F128" t="n">
-        <v>0.1019674846554346</v>
+        <v>0.05721397228193037</v>
       </c>
       <c r="G128" t="n">
-        <v>18.32637189340918</v>
+        <v>16.35428027138207</v>
       </c>
       <c r="H128" t="n">
-        <v>0.8388582046439572</v>
+        <v>0.8676930505169788</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J128" t="n">
-        <v>1.948588609695435</v>
+        <v>3.347311019897461</v>
       </c>
     </row>
     <row r="129">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>OSC_1</t>
+          <t>SNV_Detrend_SG_D1</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -5836,24 +5836,24 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.8234288764178299</v>
+        <v>0.8676930505169788</v>
       </c>
       <c r="F129" t="n">
-        <v>0.08548701811934539</v>
+        <v>0.05721397228193037</v>
       </c>
       <c r="G129" t="n">
-        <v>19.0376037977626</v>
+        <v>16.35428027138207</v>
       </c>
       <c r="H129" t="n">
-        <v>0.8234288764178299</v>
+        <v>0.8676930505169788</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J129" t="n">
-        <v>3.42303466796875</v>
+        <v>3.871074914932251</v>
       </c>
     </row>
     <row r="130">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Wavelet_Denoising</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5878,24 +5878,24 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.815473528081015</v>
+        <v>0.8673331555744669</v>
       </c>
       <c r="F130" t="n">
-        <v>0.09248843723044727</v>
+        <v>0.05722912089863422</v>
       </c>
       <c r="G130" t="n">
-        <v>19.37558440100212</v>
+        <v>16.3809745250085</v>
       </c>
       <c r="H130" t="n">
-        <v>0.815473528081015</v>
+        <v>0.8673331555744669</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J130" t="n">
-        <v>1.84044075012207</v>
+        <v>10.11510419845581</v>
       </c>
     </row>
     <row r="131">
@@ -5906,38 +5906,38 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SNV_Detrend_SG_D1</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.815473528081015</v>
+        <v>0.8657370026625699</v>
       </c>
       <c r="F131" t="n">
-        <v>0.09248843723044727</v>
+        <v>0.05352020959733033</v>
       </c>
       <c r="G131" t="n">
-        <v>19.37558440100212</v>
+        <v>16.4827280092376</v>
       </c>
       <c r="H131" t="n">
-        <v>0.815473528081015</v>
+        <v>0.8657370026625699</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+          <t>{'model__pca__n_components': 10}</t>
         </is>
       </c>
       <c r="J131" t="n">
-        <v>2.271128416061401</v>
+        <v>0.5513341426849365</v>
       </c>
     </row>
     <row r="132">
@@ -5948,38 +5948,38 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Wavelet_Denoising</t>
+          <t>SNV_Detrend_SG_D1</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.8154330191416355</v>
+        <v>0.8657369975426427</v>
       </c>
       <c r="F132" t="n">
-        <v>0.0925045045092986</v>
+        <v>0.05352020243387608</v>
       </c>
       <c r="G132" t="n">
-        <v>19.37782956336984</v>
+        <v>16.48272758254234</v>
       </c>
       <c r="H132" t="n">
-        <v>0.8154330191416355</v>
+        <v>0.8657369975426427</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+          <t>{'model__pca__n_components': 10}</t>
         </is>
       </c>
       <c r="J132" t="n">
-        <v>4.767074584960938</v>
+        <v>0.6751284599304199</v>
       </c>
     </row>
     <row r="133">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Detrend</t>
+          <t>Wavelet_Denoising</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6004,24 +6004,24 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.8117756255427515</v>
+        <v>0.8657358131730417</v>
       </c>
       <c r="F133" t="n">
-        <v>0.1384762612646155</v>
+        <v>0.05349655426086248</v>
       </c>
       <c r="G133" t="n">
-        <v>19.06832367685115</v>
+        <v>16.48292900698405</v>
       </c>
       <c r="H133" t="n">
-        <v>0.8117756255427515</v>
+        <v>0.8657358131730417</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+          <t>{'model__pca__n_components': 10}</t>
         </is>
       </c>
       <c r="J133" t="n">
-        <v>1.918354749679565</v>
+        <v>0.7066459655761719</v>
       </c>
     </row>
     <row r="134">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>Detrend</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6046,24 +6046,24 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.7870908771869218</v>
+        <v>0.8630897531621953</v>
       </c>
       <c r="F134" t="n">
-        <v>0.1454396680256004</v>
+        <v>0.0799127606356269</v>
       </c>
       <c r="G134" t="n">
-        <v>20.71315101461724</v>
+        <v>16.57169977733019</v>
       </c>
       <c r="H134" t="n">
-        <v>0.7870908771869218</v>
+        <v>0.8630897531621953</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J134" t="n">
-        <v>2.544538259506226</v>
+        <v>3.510546922683716</v>
       </c>
     </row>
     <row r="135">
@@ -6088,24 +6088,24 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.7870908771868481</v>
+        <v>0.8554353989896478</v>
       </c>
       <c r="F135" t="n">
-        <v>0.1454396680256099</v>
+        <v>0.09608626027945466</v>
       </c>
       <c r="G135" t="n">
-        <v>20.71315101462394</v>
+        <v>17.24695301556223</v>
       </c>
       <c r="H135" t="n">
-        <v>0.7870908771868481</v>
+        <v>0.8554353989896478</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J135" t="n">
-        <v>2.242814064025879</v>
+        <v>4.862148523330688</v>
       </c>
     </row>
     <row r="136">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Continuum_Removal</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6130,24 +6130,24 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.771555507637443</v>
+        <v>0.8554353989894489</v>
       </c>
       <c r="F136" t="n">
-        <v>0.1188907390236148</v>
+        <v>0.09608626027924688</v>
       </c>
       <c r="G136" t="n">
-        <v>21.31204152190779</v>
+        <v>17.24695301555883</v>
       </c>
       <c r="H136" t="n">
-        <v>0.771555507637443</v>
+        <v>0.8554353989894489</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J136" t="n">
-        <v>54.70436501502991</v>
+        <v>6.623717546463013</v>
       </c>
     </row>
     <row r="137">
@@ -6163,33 +6163,33 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Normalize</t>
+          <t>MSC_SG_OSC</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.7648958220787523</v>
+        <v>0.8476273606655654</v>
       </c>
       <c r="F137" t="n">
-        <v>0.1449039636703734</v>
+        <v>0.1495846634849805</v>
       </c>
       <c r="G137" t="n">
-        <v>22.30471088133223</v>
+        <v>17.44444883564035</v>
       </c>
       <c r="H137" t="n">
-        <v>0.7648958220787523</v>
+        <v>0.8476273606655654</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J137" t="n">
-        <v>1.786086082458496</v>
+        <v>15.53770303726196</v>
       </c>
     </row>
     <row r="138">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>Continuum_Removal</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6214,24 +6214,24 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.752842204483439</v>
+        <v>0.8445620437338872</v>
       </c>
       <c r="F138" t="n">
-        <v>0.188608181421505</v>
+        <v>0.07286444293297382</v>
       </c>
       <c r="G138" t="n">
-        <v>23.64788349141374</v>
+        <v>17.92528273683556</v>
       </c>
       <c r="H138" t="n">
-        <v>0.752842204483439</v>
+        <v>0.8445620437338872</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>{'model__n_components': 20}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J138" t="n">
-        <v>0.6654987335205078</v>
+        <v>174.1204943656921</v>
       </c>
     </row>
     <row r="139">
@@ -6242,38 +6242,38 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>EMSC</t>
+          <t>OPLS1_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.7528422044796335</v>
+        <v>0.8441857250584649</v>
       </c>
       <c r="F139" t="n">
-        <v>0.18860818142274</v>
+        <v>0.1553564011703963</v>
       </c>
       <c r="G139" t="n">
-        <v>23.64788349158764</v>
+        <v>17.592174472179</v>
       </c>
       <c r="H139" t="n">
-        <v>0.7528422044796335</v>
+        <v>0.8441857250584649</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>{'model__n_components': 20}</t>
+          <t>{'model__C': 100, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J139" t="n">
-        <v>0.7568576335906982</v>
+        <v>9.115781784057617</v>
       </c>
     </row>
     <row r="140">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SG_D2</t>
+          <t>Normalize</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6298,24 +6298,24 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.6919134619630348</v>
+        <v>0.8298298682400839</v>
       </c>
       <c r="F140" t="n">
-        <v>0.2190910121509156</v>
+        <v>0.1097788242065187</v>
       </c>
       <c r="G140" t="n">
-        <v>25.48562754206027</v>
+        <v>18.70647369671373</v>
       </c>
       <c r="H140" t="n">
-        <v>0.6919134619630348</v>
+        <v>0.8298298682400839</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 20}</t>
+          <t>{'model__C': 100, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J140" t="n">
-        <v>0.8096632957458496</v>
+        <v>3.650081396102905</v>
       </c>
     </row>
     <row r="141">
@@ -6326,38 +6326,38 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>OPLS2_SNV_SG_D1</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.6315575122040992</v>
+        <v>0.752842204483439</v>
       </c>
       <c r="F141" t="n">
-        <v>0.2775644100287432</v>
+        <v>0.188608181421505</v>
       </c>
       <c r="G141" t="n">
-        <v>26.89802969552237</v>
+        <v>23.64788349141374</v>
       </c>
       <c r="H141" t="n">
-        <v>0.6315575122040992</v>
+        <v>0.752842204483439</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__n_components': 20}</t>
         </is>
       </c>
       <c r="J141" t="n">
-        <v>4.186477422714233</v>
+        <v>0.6502737998962402</v>
       </c>
     </row>
     <row r="142">
@@ -6368,38 +6368,38 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MSC_SG_OSC</t>
+          <t>EMSC</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.4766396369564562</v>
+        <v>0.7528422044796335</v>
       </c>
       <c r="F142" t="n">
-        <v>0.3842890512095445</v>
+        <v>0.18860818142274</v>
       </c>
       <c r="G142" t="n">
-        <v>31.95234943060522</v>
+        <v>23.64788349158764</v>
       </c>
       <c r="H142" t="n">
-        <v>0.4766396369564562</v>
+        <v>0.7528422044796335</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__n_components': 20}</t>
         </is>
       </c>
       <c r="J142" t="n">
-        <v>5.217812776565552</v>
+        <v>0.5506222248077393</v>
       </c>
     </row>
     <row r="143">
@@ -6410,38 +6410,38 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>OPLS1_SNV_SG_D1</t>
+          <t>SG_D2</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.4717332353856863</v>
+        <v>0.6910639171392192</v>
       </c>
       <c r="F143" t="n">
-        <v>0.3832530194562629</v>
+        <v>0.2196402051000372</v>
       </c>
       <c r="G143" t="n">
-        <v>32.14938297956795</v>
+        <v>25.49211268052612</v>
       </c>
       <c r="H143" t="n">
-        <v>0.4717332353856863</v>
+        <v>0.6910639171392192</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__pca__n_components': 20}</t>
         </is>
       </c>
       <c r="J143" t="n">
-        <v>3.869517087936401</v>
+        <v>0.6647188663482666</v>
       </c>
     </row>
     <row r="144">
@@ -6466,24 +6466,24 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.0868165227291921</v>
+        <v>0.6327396703801454</v>
       </c>
       <c r="F144" t="n">
-        <v>0.6153553157048671</v>
+        <v>0.2327019548481674</v>
       </c>
       <c r="G144" t="n">
-        <v>42.01514985249398</v>
+        <v>26.97078151639752</v>
       </c>
       <c r="H144" t="n">
-        <v>0.0868165227291921</v>
+        <v>0.6327396703801454</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J144" t="n">
-        <v>1.704125642776489</v>
+        <v>3.947719097137451</v>
       </c>
     </row>
     <row r="145">
@@ -6508,24 +6508,24 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>-0.5957307328583834</v>
+        <v>0.5221651753879576</v>
       </c>
       <c r="F145" t="n">
-        <v>0.92095198339656</v>
+        <v>0.3355684725122635</v>
       </c>
       <c r="G145" t="n">
-        <v>55.91270694244497</v>
+        <v>30.51888830685184</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.5957307328583834</v>
+        <v>0.5221651753879576</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J145" t="n">
-        <v>2.484976530075073</v>
+        <v>4.014097452163696</v>
       </c>
     </row>
     <row r="146">
@@ -6550,16 +6550,16 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.5189957231067505</v>
+        <v>0.5191985757103706</v>
       </c>
       <c r="F146" t="n">
-        <v>0.4383857873918581</v>
+        <v>0.438571281163816</v>
       </c>
       <c r="G146" t="n">
-        <v>0.09377405702846389</v>
+        <v>0.09375732444904841</v>
       </c>
       <c r="H146" t="n">
-        <v>0.5189957231067505</v>
+        <v>0.5191985757103706</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>0.7192950248718262</v>
+        <v>0.6984958648681641</v>
       </c>
     </row>
     <row r="147">
@@ -6609,7 +6609,7 @@
         </is>
       </c>
       <c r="J147" t="n">
-        <v>4.388075113296509</v>
+        <v>9.879589796066284</v>
       </c>
     </row>
     <row r="148">
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>4.045970678329468</v>
+        <v>7.87994122505188</v>
       </c>
     </row>
     <row r="149">
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>4.807575225830078</v>
+        <v>13.06728959083557</v>
       </c>
     </row>
     <row r="150">
@@ -6718,16 +6718,16 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.4565789446353777</v>
+        <v>0.4564770287985566</v>
       </c>
       <c r="F150" t="n">
-        <v>0.6097309266264145</v>
+        <v>0.6098070915258235</v>
       </c>
       <c r="G150" t="n">
-        <v>0.09815244871424396</v>
+        <v>0.09814664483872472</v>
       </c>
       <c r="H150" t="n">
-        <v>0.4565789446353777</v>
+        <v>0.4564770287985566</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="J150" t="n">
-        <v>0.9852113723754883</v>
+        <v>0.7429521083831787</v>
       </c>
     </row>
     <row r="151">
@@ -6760,16 +6760,16 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.447043221742073</v>
+        <v>0.4471763626008589</v>
       </c>
       <c r="F151" t="n">
-        <v>0.6355295729512973</v>
+        <v>0.635331568259085</v>
       </c>
       <c r="G151" t="n">
-        <v>0.09857405604448478</v>
+        <v>0.09856992243044985</v>
       </c>
       <c r="H151" t="n">
-        <v>0.447043221742073</v>
+        <v>0.4471763626008589</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="J151" t="n">
-        <v>1.140364170074463</v>
+        <v>0.8705189228057861</v>
       </c>
     </row>
     <row r="152">
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="J152" t="n">
-        <v>1.997584104537964</v>
+        <v>3.262333393096924</v>
       </c>
     </row>
     <row r="153">
@@ -6861,7 +6861,7 @@
         </is>
       </c>
       <c r="J153" t="n">
-        <v>0.9225552082061768</v>
+        <v>0.8215348720550537</v>
       </c>
     </row>
     <row r="154">
@@ -6872,38 +6872,38 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>SG_D2</t>
+          <t>OSC_2</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.410108881634866</v>
+        <v>0.4119636370375978</v>
       </c>
       <c r="F154" t="n">
-        <v>0.6621904221193339</v>
+        <v>0.5281248796188961</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0989388077566504</v>
+        <v>0.1097401107842598</v>
       </c>
       <c r="H154" t="n">
-        <v>0.410108881634866</v>
+        <v>0.4119636370375978</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>{'model__n_components': 5}</t>
+          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'auto', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J154" t="n">
-        <v>0.8340790271759033</v>
+        <v>6.271661996841431</v>
       </c>
     </row>
     <row r="155">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SG_D1</t>
+          <t>SG_D2</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -6928,24 +6928,24 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.4095228730353017</v>
+        <v>0.410108881634866</v>
       </c>
       <c r="F155" t="n">
-        <v>0.5041003158618006</v>
+        <v>0.6621904221193339</v>
       </c>
       <c r="G155" t="n">
-        <v>0.1066181550803837</v>
+        <v>0.0989388077566504</v>
       </c>
       <c r="H155" t="n">
-        <v>0.4095228730353017</v>
+        <v>0.410108881634866</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>{'model__C': 1, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__n_components': 5}</t>
         </is>
       </c>
       <c r="J155" t="n">
-        <v>2.113853931427002</v>
+        <v>0.5829315185546875</v>
       </c>
     </row>
     <row r="156">
@@ -6961,33 +6961,33 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>OSC_2</t>
+          <t>SG_D1</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.4093414293897978</v>
+        <v>0.4095228730353017</v>
       </c>
       <c r="F156" t="n">
-        <v>0.6172757070328084</v>
+        <v>0.5041003158618006</v>
       </c>
       <c r="G156" t="n">
-        <v>0.1062132397945266</v>
+        <v>0.1066181550803837</v>
       </c>
       <c r="H156" t="n">
-        <v>0.4093414293897978</v>
+        <v>0.4095228730353017</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>{'model__C': 0.1, 'model__epsilon': 0.1, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 1, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>3.677820444107056</v>
+        <v>3.572989225387573</v>
       </c>
     </row>
     <row r="157">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>MSC_SG_OSC</t>
+          <t>OSC_1</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7012,24 +7012,24 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.3999807434130054</v>
+        <v>0.405757608908746</v>
       </c>
       <c r="F157" t="n">
-        <v>0.7825700009144576</v>
+        <v>0.5195947649234366</v>
       </c>
       <c r="G157" t="n">
-        <v>0.1008197652577235</v>
+        <v>0.1113741114264773</v>
       </c>
       <c r="H157" t="n">
-        <v>0.3999807434130054</v>
+        <v>0.405757608908746</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>{'model__n_components': 5}</t>
+          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'auto', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J157" t="n">
-        <v>1.199877262115479</v>
+        <v>4.466368675231934</v>
       </c>
     </row>
     <row r="158">
@@ -7040,38 +7040,38 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>MSC_SG_OSC</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.3991081752107056</v>
+        <v>0.3999807434130054</v>
       </c>
       <c r="F158" t="n">
-        <v>0.2673311745823104</v>
+        <v>0.7825700009144576</v>
       </c>
       <c r="G158" t="n">
-        <v>0.1168417600388688</v>
+        <v>0.1008197652577235</v>
       </c>
       <c r="H158" t="n">
-        <v>0.3991081752107056</v>
+        <v>0.3999807434130054</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>{'model__C': 0.1, 'model__epsilon': 0.1, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__n_components': 5}</t>
         </is>
       </c>
       <c r="J158" t="n">
-        <v>2.300074100494385</v>
+        <v>0.9585115909576416</v>
       </c>
     </row>
     <row r="159">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>EMSC</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7096,16 +7096,16 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.3991081752107053</v>
+        <v>0.3991081752107056</v>
       </c>
       <c r="F159" t="n">
-        <v>0.2673311745823098</v>
+        <v>0.2673311745823104</v>
       </c>
       <c r="G159" t="n">
-        <v>0.1168417600388689</v>
+        <v>0.1168417600388688</v>
       </c>
       <c r="H159" t="n">
-        <v>0.3991081752107053</v>
+        <v>0.3991081752107056</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>1.905118942260742</v>
+        <v>6.475599765777588</v>
       </c>
     </row>
     <row r="160">
@@ -7124,38 +7124,38 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>OPLS2_SNV_SG_D1</t>
+          <t>EMSC</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.3957120210140759</v>
+        <v>0.3991081752107053</v>
       </c>
       <c r="F160" t="n">
-        <v>0.7569565365779095</v>
+        <v>0.2673311745823098</v>
       </c>
       <c r="G160" t="n">
-        <v>0.1024582858290481</v>
+        <v>0.1168417600388689</v>
       </c>
       <c r="H160" t="n">
-        <v>0.3957120210140759</v>
+        <v>0.3991081752107053</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 10}</t>
+          <t>{'model__C': 0.1, 'model__epsilon': 0.1, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J160" t="n">
-        <v>0.9778125286102295</v>
+        <v>4.321666717529297</v>
       </c>
     </row>
     <row r="161">
@@ -7166,12 +7166,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SG_D1</t>
+          <t>SNV</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7180,24 +7180,24 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.3931286530733878</v>
+        <v>0.3962141699281023</v>
       </c>
       <c r="F161" t="n">
-        <v>0.6896092383365185</v>
+        <v>0.3080813377021104</v>
       </c>
       <c r="G161" t="n">
-        <v>0.09975958797387099</v>
+        <v>0.118486054624911</v>
       </c>
       <c r="H161" t="n">
-        <v>0.3931286530733878</v>
+        <v>0.3962141699281023</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>{'model__n_components': 5}</t>
+          <t>{'model__C': 1, 'model__epsilon': 0.1, 'model__gamma': 0.001, 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J161" t="n">
-        <v>0.7947866916656494</v>
+        <v>3.419471263885498</v>
       </c>
     </row>
     <row r="162">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>OSC_1</t>
+          <t>OPLS2_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7222,24 +7222,24 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.3839879992402643</v>
+        <v>0.3957298711092756</v>
       </c>
       <c r="F162" t="n">
-        <v>0.5722730598533227</v>
+        <v>0.7570016018803556</v>
       </c>
       <c r="G162" t="n">
-        <v>0.1097814672457542</v>
+        <v>0.1024617172154066</v>
       </c>
       <c r="H162" t="n">
-        <v>0.3839879992402643</v>
+        <v>0.3957298711092756</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>{'model__C': 0.1, 'model__epsilon': 0.1, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__pca__n_components': 10}</t>
         </is>
       </c>
       <c r="J162" t="n">
-        <v>3.846582412719727</v>
+        <v>0.7933950424194336</v>
       </c>
     </row>
     <row r="163">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>SNV</t>
+          <t>SG_D1</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7264,24 +7264,24 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.3748702040397605</v>
+        <v>0.3931286530733878</v>
       </c>
       <c r="F163" t="n">
-        <v>0.2657414231976329</v>
+        <v>0.6896092383365185</v>
       </c>
       <c r="G163" t="n">
-        <v>0.1206163547154965</v>
+        <v>0.09975958797387099</v>
       </c>
       <c r="H163" t="n">
-        <v>0.3748702040397605</v>
+        <v>0.3931286530733878</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>{'model__C': 0.1, 'model__epsilon': 0.1, 'model__gamma': 0.01, 'model__kernel': 'rbf'}</t>
+          <t>{'model__n_components': 5}</t>
         </is>
       </c>
       <c r="J163" t="n">
-        <v>2.03255033493042</v>
+        <v>0.5863492488861084</v>
       </c>
     </row>
     <row r="164">
@@ -7292,12 +7292,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SG_D1</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7306,24 +7306,24 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.3719116878164603</v>
+        <v>0.3861769543764644</v>
       </c>
       <c r="F164" t="n">
-        <v>0.6221822393967218</v>
+        <v>0.5085704618706849</v>
       </c>
       <c r="G164" t="n">
-        <v>0.1053024931253173</v>
+        <v>0.1137323632559061</v>
       </c>
       <c r="H164" t="n">
-        <v>0.3719116878164603</v>
+        <v>0.3861769543764644</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 5}</t>
+          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'auto', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J164" t="n">
-        <v>0.7466919422149658</v>
+        <v>2.907887697219849</v>
       </c>
     </row>
     <row r="165">
@@ -7339,33 +7339,33 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Detrend</t>
+          <t>SNV_Detrend_SG_D1</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.3712411819726997</v>
+        <v>0.3861769543764644</v>
       </c>
       <c r="F165" t="n">
-        <v>0.4435674819395523</v>
+        <v>0.5085704618706849</v>
       </c>
       <c r="G165" t="n">
-        <v>0.1124998808913322</v>
+        <v>0.1137323632559061</v>
       </c>
       <c r="H165" t="n">
-        <v>0.3712411819726997</v>
+        <v>0.3861769543764644</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>{'model__C': 0.1, 'model__epsilon': 0.1, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'auto', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J165" t="n">
-        <v>2.078571557998657</v>
+        <v>2.854219198226929</v>
       </c>
     </row>
     <row r="166">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SG_D2</t>
+          <t>Wavelet_Denoising</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -7390,24 +7390,24 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.3639889201936154</v>
+        <v>0.3861322768279104</v>
       </c>
       <c r="F166" t="n">
-        <v>0.5274031562791256</v>
+        <v>0.5086073433180969</v>
       </c>
       <c r="G166" t="n">
-        <v>0.1065038870991914</v>
+        <v>0.1137451485255541</v>
       </c>
       <c r="H166" t="n">
-        <v>0.3639889201936154</v>
+        <v>0.3861322768279104</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'auto', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J166" t="n">
-        <v>1.837685823440552</v>
+        <v>8.748539447784424</v>
       </c>
     </row>
     <row r="167">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Continuum_Removal</t>
+          <t>Detrend</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -7432,24 +7432,24 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.3631737672015591</v>
+        <v>0.379452611630206</v>
       </c>
       <c r="F167" t="n">
-        <v>0.5298973486085301</v>
+        <v>0.3762062977941202</v>
       </c>
       <c r="G167" t="n">
-        <v>0.1126532864244752</v>
+        <v>0.1167234840575104</v>
       </c>
       <c r="H167" t="n">
-        <v>0.3631737672015591</v>
+        <v>0.379452611630206</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>{'model__C': 1, 'model__epsilon': 0.1, 'model__gamma': 0.01, 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'auto', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J167" t="n">
-        <v>55.54982233047485</v>
+        <v>2.955923080444336</v>
       </c>
     </row>
     <row r="168">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Wavelet_Denoising</t>
+          <t>SG_D1</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -7474,24 +7474,24 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.3629667462382749</v>
+        <v>0.3719116878885316</v>
       </c>
       <c r="F168" t="n">
-        <v>0.4469186576612804</v>
+        <v>0.6221822393692784</v>
       </c>
       <c r="G168" t="n">
-        <v>0.112584268970069</v>
+        <v>0.1053024931277769</v>
       </c>
       <c r="H168" t="n">
-        <v>0.3629667462382749</v>
+        <v>0.3719116878885316</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>{'model__C': 0.1, 'model__epsilon': 0.1, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__pca__n_components': 5}</t>
         </is>
       </c>
       <c r="J168" t="n">
-        <v>3.804486751556396</v>
+        <v>0.7382979393005371</v>
       </c>
     </row>
     <row r="169">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>SG_D2</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -7516,24 +7516,24 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.3628220263092451</v>
+        <v>0.3639889201936154</v>
       </c>
       <c r="F169" t="n">
-        <v>0.4470334857400147</v>
+        <v>0.5274031562791256</v>
       </c>
       <c r="G169" t="n">
-        <v>0.1125966957204303</v>
+        <v>0.1065038870991914</v>
       </c>
       <c r="H169" t="n">
-        <v>0.3628220263092451</v>
+        <v>0.3639889201936154</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>{'model__C': 0.1, 'model__epsilon': 0.1, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>2.080331325531006</v>
+        <v>3.555500507354736</v>
       </c>
     </row>
     <row r="170">
@@ -7549,33 +7549,33 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SNV_Detrend_SG_D1</t>
+          <t>Continuum_Removal</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.3628220263092451</v>
+        <v>0.3631737672015591</v>
       </c>
       <c r="F170" t="n">
-        <v>0.4470334857400147</v>
+        <v>0.5298973486085301</v>
       </c>
       <c r="G170" t="n">
-        <v>0.1125966957204303</v>
+        <v>0.1126532864244752</v>
       </c>
       <c r="H170" t="n">
-        <v>0.3628220263092451</v>
+        <v>0.3631737672015591</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>{'model__C': 0.1, 'model__epsilon': 0.1, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 1, 'model__epsilon': 0.1, 'model__gamma': 0.01, 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J170" t="n">
-        <v>2.178605079650879</v>
+        <v>179.2652111053467</v>
       </c>
     </row>
     <row r="171">
@@ -7600,16 +7600,16 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.3622870791291549</v>
+        <v>0.3622870791291437</v>
       </c>
       <c r="F171" t="n">
-        <v>0.571490730549388</v>
+        <v>0.5714907305494028</v>
       </c>
       <c r="G171" t="n">
         <v>0.1079717347316058</v>
       </c>
       <c r="H171" t="n">
-        <v>0.3622870791291549</v>
+        <v>0.3622870791291437</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>0.7549166679382324</v>
+        <v>0.7335731983184814</v>
       </c>
     </row>
     <row r="172">
@@ -7642,16 +7642,16 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.3522815216485949</v>
+        <v>0.3520433153080174</v>
       </c>
       <c r="F172" t="n">
-        <v>0.8315420154791604</v>
+        <v>0.8320241089745516</v>
       </c>
       <c r="G172" t="n">
-        <v>0.1057278407558995</v>
+        <v>0.1057478533209528</v>
       </c>
       <c r="H172" t="n">
-        <v>0.3522815216485949</v>
+        <v>0.3520433153080174</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         </is>
       </c>
       <c r="J172" t="n">
-        <v>0.7461402416229248</v>
+        <v>0.6948142051696777</v>
       </c>
     </row>
     <row r="173">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>EMSC</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -7684,16 +7684,16 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>0.3487000761101012</v>
+        <v>0.3486095511423055</v>
       </c>
       <c r="F173" t="n">
-        <v>0.8633021582204895</v>
+        <v>0.8635896285605069</v>
       </c>
       <c r="G173" t="n">
-        <v>0.1040115787353022</v>
+        <v>0.1039857349397782</v>
       </c>
       <c r="H173" t="n">
-        <v>0.3487000761101012</v>
+        <v>0.3486095511423055</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>0.8978188037872314</v>
+        <v>0.7265477180480957</v>
       </c>
     </row>
     <row r="174">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>EMSC</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -7726,16 +7726,16 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>0.3482408008656138</v>
+        <v>0.3482728254094336</v>
       </c>
       <c r="F174" t="n">
-        <v>0.863558502673417</v>
+        <v>0.8637747668845345</v>
       </c>
       <c r="G174" t="n">
-        <v>0.1040977713692846</v>
+        <v>0.1040193768493358</v>
       </c>
       <c r="H174" t="n">
-        <v>0.3482408008656138</v>
+        <v>0.3482728254094336</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="J174" t="n">
-        <v>0.751523494720459</v>
+        <v>0.8184981346130371</v>
       </c>
     </row>
     <row r="175">
@@ -7768,16 +7768,16 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>0.3324304050179386</v>
+        <v>0.3324304050179364</v>
       </c>
       <c r="F175" t="n">
-        <v>0.6141267436066846</v>
+        <v>0.6141267436066906</v>
       </c>
       <c r="G175" t="n">
         <v>0.1095738227419534</v>
       </c>
       <c r="H175" t="n">
-        <v>0.3324304050179386</v>
+        <v>0.3324304050179364</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="J175" t="n">
-        <v>0.7453858852386475</v>
+        <v>0.6972486972808838</v>
       </c>
     </row>
     <row r="176">
@@ -7810,16 +7810,16 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>0.2783282210557626</v>
+        <v>0.2783282210557657</v>
       </c>
       <c r="F176" t="n">
-        <v>1.083019433063534</v>
+        <v>1.083019433063525</v>
       </c>
       <c r="G176" t="n">
         <v>0.1080998017810432</v>
       </c>
       <c r="H176" t="n">
-        <v>0.2783282210557626</v>
+        <v>0.2783282210557657</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         </is>
       </c>
       <c r="J176" t="n">
-        <v>0.8993041515350342</v>
+        <v>0.6438667774200439</v>
       </c>
     </row>
     <row r="177">
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>0.2783282210557594</v>
+        <v>0.2783282210557593</v>
       </c>
       <c r="F177" t="n">
         <v>1.083019433063546</v>
@@ -7861,7 +7861,7 @@
         <v>0.1080998017810433</v>
       </c>
       <c r="H177" t="n">
-        <v>0.2783282210557594</v>
+        <v>0.2783282210557593</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         </is>
       </c>
       <c r="J177" t="n">
-        <v>0.8099770545959473</v>
+        <v>0.6816511154174805</v>
       </c>
     </row>
     <row r="178">
@@ -7894,16 +7894,16 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>0.2783242313097359</v>
+        <v>0.2783242313097308</v>
       </c>
       <c r="F178" t="n">
-        <v>1.083033337215868</v>
+        <v>1.08303333721588</v>
       </c>
       <c r="G178" t="n">
         <v>0.1080999914686575</v>
       </c>
       <c r="H178" t="n">
-        <v>0.2783242313097359</v>
+        <v>0.2783242313097308</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="J178" t="n">
-        <v>0.9813148975372314</v>
+        <v>0.7950804233551025</v>
       </c>
     </row>
     <row r="179">
@@ -7936,16 +7936,16 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>0.2750515612294365</v>
+        <v>0.2750515612294376</v>
       </c>
       <c r="F179" t="n">
-        <v>0.9297307862797187</v>
+        <v>0.9297307862797156</v>
       </c>
       <c r="G179" t="n">
-        <v>0.1073647940170688</v>
+        <v>0.1073647940170687</v>
       </c>
       <c r="H179" t="n">
-        <v>0.2750515612294365</v>
+        <v>0.2750515612294376</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>0.9034335613250732</v>
+        <v>0.659339427947998</v>
       </c>
     </row>
     <row r="180">
@@ -7995,7 +7995,7 @@
         </is>
       </c>
       <c r="J180" t="n">
-        <v>0.898714542388916</v>
+        <v>0.8616626262664795</v>
       </c>
     </row>
     <row r="181">
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="J181" t="n">
-        <v>0.8734533786773682</v>
+        <v>0.5775079727172852</v>
       </c>
     </row>
     <row r="182">
@@ -8079,7 +8079,7 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>0.8463008403778076</v>
+        <v>0.5717253684997559</v>
       </c>
     </row>
     <row r="183">
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>0.8139426708221436</v>
+        <v>0.7078232765197754</v>
       </c>
     </row>
     <row r="184">
@@ -8146,16 +8146,16 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>0.1724972541746004</v>
+        <v>0.1725574000687221</v>
       </c>
       <c r="F184" t="n">
-        <v>1.38584469684605</v>
+        <v>1.385222160126996</v>
       </c>
       <c r="G184" t="n">
-        <v>0.1094759857396535</v>
+        <v>0.1094586382762291</v>
       </c>
       <c r="H184" t="n">
-        <v>0.1724972541746004</v>
+        <v>0.1725574000687221</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         </is>
       </c>
       <c r="J184" t="n">
-        <v>0.9498889446258545</v>
+        <v>0.7146027088165283</v>
       </c>
     </row>
     <row r="185">
@@ -8188,16 +8188,16 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>0.1493174431552151</v>
+        <v>0.1493175584472011</v>
       </c>
       <c r="F185" t="n">
-        <v>1.419313429735563</v>
+        <v>1.41931358986368</v>
       </c>
       <c r="G185" t="n">
-        <v>0.1122831037041216</v>
+        <v>0.1122827050286575</v>
       </c>
       <c r="H185" t="n">
-        <v>0.1493174431552151</v>
+        <v>0.1493175584472011</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="J185" t="n">
-        <v>7.916110038757324</v>
+        <v>6.669434547424316</v>
       </c>
     </row>
     <row r="186">
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>0.8248124122619629</v>
+        <v>0.5518150329589844</v>
       </c>
     </row>
     <row r="187">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="J187" t="n">
-        <v>0.7209360599517822</v>
+        <v>0.9104166030883789</v>
       </c>
     </row>
     <row r="188">
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="J188" t="n">
-        <v>0.9564800262451172</v>
+        <v>0.7967555522918701</v>
       </c>
     </row>
     <row r="189">
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="J189" t="n">
-        <v>0.928746223449707</v>
+        <v>0.7544112205505371</v>
       </c>
     </row>
     <row r="190">
@@ -8415,7 +8415,7 @@
         </is>
       </c>
       <c r="J190" t="n">
-        <v>7.410459280014038</v>
+        <v>6.379380464553833</v>
       </c>
     </row>
     <row r="191">
@@ -8457,7 +8457,7 @@
         </is>
       </c>
       <c r="J191" t="n">
-        <v>0.9892771244049072</v>
+        <v>0.5649683475494385</v>
       </c>
     </row>
     <row r="192">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="J192" t="n">
-        <v>0.8662052154541016</v>
+        <v>0.6302833557128906</v>
       </c>
     </row>
     <row r="193">
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>0.8405697345733643</v>
+        <v>0.5844848155975342</v>
       </c>
     </row>
     <row r="194">
@@ -8552,38 +8552,38 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>MSC_SG_OSC</t>
+          <t>SG_D2</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>0.1362716853525399</v>
+        <v>0.1424805835154034</v>
       </c>
       <c r="F194" t="n">
-        <v>0.9319398520070221</v>
+        <v>0.5115143065425179</v>
       </c>
       <c r="G194" t="n">
-        <v>1.042305974022729</v>
+        <v>1.105221248109896</v>
       </c>
       <c r="H194" t="n">
-        <v>0.1362716853525399</v>
+        <v>0.1424805835154034</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 10}</t>
+          <t>{'model__C': 100, 'model__epsilon': 0.2, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J194" t="n">
-        <v>1.5637366771698</v>
+        <v>3.791992664337158</v>
       </c>
     </row>
     <row r="195">
@@ -8594,38 +8594,38 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Wavelet_Denoising</t>
+          <t>MSC_SG_OSC</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>0.1066550356731658</v>
+        <v>0.1363742689534463</v>
       </c>
       <c r="F195" t="n">
-        <v>0.5551461721347651</v>
+        <v>0.9316815252323671</v>
       </c>
       <c r="G195" t="n">
-        <v>1.136056211526546</v>
+        <v>1.042376476487904</v>
       </c>
       <c r="H195" t="n">
-        <v>0.1066550356731658</v>
+        <v>0.1363742689534463</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>{'model__C': 1, 'model__epsilon': 0.5, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__pca__n_components': 10}</t>
         </is>
       </c>
       <c r="J195" t="n">
-        <v>3.399066686630249</v>
+        <v>0.837960958480835</v>
       </c>
     </row>
     <row r="196">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Wavelet_Denoising</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -8650,16 +8650,16 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>0.1066353150543823</v>
+        <v>0.1066550356731658</v>
       </c>
       <c r="F196" t="n">
-        <v>0.5551401815668701</v>
+        <v>0.5551461721347651</v>
       </c>
       <c r="G196" t="n">
-        <v>1.136090086695603</v>
+        <v>1.136056211526546</v>
       </c>
       <c r="H196" t="n">
-        <v>0.1066353150543823</v>
+        <v>0.1066550356731658</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         </is>
       </c>
       <c r="J196" t="n">
-        <v>2.161602258682251</v>
+        <v>9.008599042892456</v>
       </c>
     </row>
     <row r="197">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>SNV_Detrend_SG_D1</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="J197" t="n">
-        <v>1.970922470092773</v>
+        <v>3.703948974609375</v>
       </c>
     </row>
     <row r="198">
@@ -8725,33 +8725,33 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>SG_D2</t>
+          <t>SNV_Detrend_SG_D1</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>0.09247954406823895</v>
+        <v>0.1066353150543823</v>
       </c>
       <c r="F198" t="n">
-        <v>0.4972148251427454</v>
+        <v>0.5551401815668701</v>
       </c>
       <c r="G198" t="n">
-        <v>1.152427734522779</v>
+        <v>1.136090086695603</v>
       </c>
       <c r="H198" t="n">
-        <v>0.09247954406823895</v>
+        <v>0.1066353150543823</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 1, 'model__epsilon': 0.5, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J198" t="n">
-        <v>2.433340787887573</v>
+        <v>3.720828294754028</v>
       </c>
     </row>
     <row r="199">
@@ -8762,38 +8762,38 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>OPLS1_SNV_SG_D1</t>
+          <t>SG_D1</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>0.06908689758845597</v>
+        <v>0.07401422416866014</v>
       </c>
       <c r="F199" t="n">
-        <v>1.138523647636367</v>
+        <v>0.7387806135100142</v>
       </c>
       <c r="G199" t="n">
-        <v>1.058853879574874</v>
+        <v>1.118252035545349</v>
       </c>
       <c r="H199" t="n">
-        <v>0.06908689758845597</v>
+        <v>0.07401422416866014</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 10}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J199" t="n">
-        <v>1.271890163421631</v>
+        <v>3.756802320480347</v>
       </c>
     </row>
     <row r="200">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>OPLS2_SNV_SG_D1</t>
+          <t>OPLS1_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -8818,16 +8818,16 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>0.03466033365538043</v>
+        <v>0.06891605351548222</v>
       </c>
       <c r="F200" t="n">
-        <v>0.9452793434196192</v>
+        <v>1.139007780827296</v>
       </c>
       <c r="G200" t="n">
-        <v>1.141247222192946</v>
+        <v>1.058865563685772</v>
       </c>
       <c r="H200" t="n">
-        <v>0.03466033365538043</v>
+        <v>0.06891605351548222</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         </is>
       </c>
       <c r="J200" t="n">
-        <v>2.566260814666748</v>
+        <v>0.7067553997039795</v>
       </c>
     </row>
     <row r="201">
@@ -8846,38 +8846,38 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Detrend</t>
+          <t>OPLS2_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>-0.005101716390767818</v>
+        <v>0.03471911614947589</v>
       </c>
       <c r="F201" t="n">
-        <v>0.7564706633456278</v>
+        <v>0.9451346590399411</v>
       </c>
       <c r="G201" t="n">
-        <v>1.18829979680818</v>
+        <v>1.141245652907886</v>
       </c>
       <c r="H201" t="n">
-        <v>-0.005101716390767818</v>
+        <v>0.03471911614947589</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>{'model__C': 1, 'model__epsilon': 0.1, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__pca__n_components': 10}</t>
         </is>
       </c>
       <c r="J201" t="n">
-        <v>1.823874950408936</v>
+        <v>0.7601971626281738</v>
       </c>
     </row>
     <row r="202">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>EMSC</t>
+          <t>SNV</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -8902,24 +8902,24 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>-0.02218919704935236</v>
+        <v>0.02673520721552183</v>
       </c>
       <c r="F202" t="n">
-        <v>0.6843789520269601</v>
+        <v>0.699076358043445</v>
       </c>
       <c r="G202" t="n">
-        <v>1.225502084001284</v>
+        <v>1.207021095924221</v>
       </c>
       <c r="H202" t="n">
-        <v>-0.02218919704935236</v>
+        <v>0.02673520721552183</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>{'model__C': 1, 'model__epsilon': 0.1, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 1, 'model__epsilon': 1.0, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J202" t="n">
-        <v>2.701327562332153</v>
+        <v>4.210078239440918</v>
       </c>
     </row>
     <row r="203">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>Detrend</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -8944,24 +8944,24 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>-0.02218919704935511</v>
+        <v>0.02162793862143325</v>
       </c>
       <c r="F203" t="n">
-        <v>0.6843789520269621</v>
+        <v>0.665656599896786</v>
       </c>
       <c r="G203" t="n">
-        <v>1.225502084001285</v>
+        <v>1.167954450483675</v>
       </c>
       <c r="H203" t="n">
-        <v>-0.02218919704935511</v>
+        <v>0.02162793862143325</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>{'model__C': 1, 'model__epsilon': 0.1, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 0.001, 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J203" t="n">
-        <v>3.73475980758667</v>
+        <v>3.484466552734375</v>
       </c>
     </row>
     <row r="204">
@@ -8972,38 +8972,38 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PLSR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>SG_D2</t>
+          <t>MSC_SG_OSC</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>-0.03088445354393228</v>
+        <v>-0.008296029220663493</v>
       </c>
       <c r="F204" t="n">
-        <v>0.6540207243992751</v>
+        <v>0.6661218989208789</v>
       </c>
       <c r="G204" t="n">
-        <v>1.147570218500516</v>
+        <v>1.172799620204651</v>
       </c>
       <c r="H204" t="n">
-        <v>-0.03088445354393228</v>
+        <v>-0.008296029220663493</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>{'model__n_components': 5}</t>
+          <t>{'model__C': 100, 'model__epsilon': 1.0, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J204" t="n">
-        <v>0.8019833564758301</v>
+        <v>12.85940051078796</v>
       </c>
     </row>
     <row r="205">
@@ -9014,12 +9014,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>SG_D1</t>
+          <t>EMSC</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -9028,24 +9028,24 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>-0.05535534643804383</v>
+        <v>-0.02218919704935236</v>
       </c>
       <c r="F205" t="n">
-        <v>1.402374975168078</v>
+        <v>0.6843789520269601</v>
       </c>
       <c r="G205" t="n">
-        <v>1.109173146836646</v>
+        <v>1.225502084001284</v>
       </c>
       <c r="H205" t="n">
-        <v>-0.05535534643804383</v>
+        <v>-0.02218919704935236</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 10}</t>
+          <t>{'model__C': 1, 'model__epsilon': 0.1, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J205" t="n">
-        <v>0.931875467300415</v>
+        <v>4.801983833312988</v>
       </c>
     </row>
     <row r="206">
@@ -9061,33 +9061,33 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>MSC_SG_OSC</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>-0.06112410946416182</v>
+        <v>-0.02218919704935511</v>
       </c>
       <c r="F206" t="n">
-        <v>0.7141657085606324</v>
+        <v>0.6843789520269621</v>
       </c>
       <c r="G206" t="n">
-        <v>1.19174715167597</v>
+        <v>1.225502084001285</v>
       </c>
       <c r="H206" t="n">
-        <v>-0.06112410946416182</v>
+        <v>-0.02218919704935511</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 1, 'model__epsilon': 0.1, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J206" t="n">
-        <v>4.068210601806641</v>
+        <v>6.428843021392822</v>
       </c>
     </row>
     <row r="207">
@@ -9098,12 +9098,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PLSR</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>SNV</t>
+          <t>SG_D2</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -9112,24 +9112,24 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>-0.06571891051726156</v>
+        <v>-0.03088445354393228</v>
       </c>
       <c r="F207" t="n">
-        <v>0.6226546773116397</v>
+        <v>0.6540207243992751</v>
       </c>
       <c r="G207" t="n">
-        <v>1.262615707054503</v>
+        <v>1.147570218500516</v>
       </c>
       <c r="H207" t="n">
-        <v>-0.06571891051726156</v>
+        <v>-0.03088445354393228</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>{'model__C': 1, 'model__epsilon': 0.1, 'model__gamma': 0.01, 'model__kernel': 'rbf'}</t>
+          <t>{'model__n_components': 5}</t>
         </is>
       </c>
       <c r="J207" t="n">
-        <v>2.111827850341797</v>
+        <v>0.5598502159118652</v>
       </c>
     </row>
     <row r="208">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>OSC_2</t>
+          <t>OPLS2_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -9154,24 +9154,24 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>-0.0659537133439882</v>
+        <v>-0.0464451419449147</v>
       </c>
       <c r="F208" t="n">
-        <v>1.086934683680112</v>
+        <v>0.8202877513303737</v>
       </c>
       <c r="G208" t="n">
-        <v>1.162590501443817</v>
+        <v>1.19323121346799</v>
       </c>
       <c r="H208" t="n">
-        <v>-0.0659537133439882</v>
+        <v>-0.0464451419449147</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>{'model__C': 1, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J208" t="n">
-        <v>2.580201148986816</v>
+        <v>9.221105337142944</v>
       </c>
     </row>
     <row r="209">
@@ -9182,38 +9182,38 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>OPLS2_SNV_SG_D1</t>
+          <t>SG_D1</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>-0.06725271643129875</v>
+        <v>-0.0551769351991807</v>
       </c>
       <c r="F209" t="n">
-        <v>0.8405797428597005</v>
+        <v>1.402052909613621</v>
       </c>
       <c r="G209" t="n">
-        <v>1.15699461407607</v>
+        <v>1.109151231871791</v>
       </c>
       <c r="H209" t="n">
-        <v>-0.06725271643129875</v>
+        <v>-0.0551769351991807</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__pca__n_components': 10}</t>
         </is>
       </c>
       <c r="J209" t="n">
-        <v>3.251399517059326</v>
+        <v>0.6079921722412109</v>
       </c>
     </row>
     <row r="210">
@@ -9229,33 +9229,33 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Continuum_Removal</t>
+          <t>OSC_2</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>-0.07042647827390093</v>
+        <v>-0.0659537133439882</v>
       </c>
       <c r="F210" t="n">
-        <v>0.6960500610470221</v>
+        <v>1.086934683680112</v>
       </c>
       <c r="G210" t="n">
-        <v>1.237328757926025</v>
+        <v>1.162590501443817</v>
       </c>
       <c r="H210" t="n">
-        <v>-0.07042647827390093</v>
+        <v>-0.0659537133439882</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>{'model__C': 1, 'model__epsilon': 0.1, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 1, 'model__epsilon': 0.5, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J210" t="n">
-        <v>53.00392389297485</v>
+        <v>6.014701843261719</v>
       </c>
     </row>
     <row r="211">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Normalize</t>
+          <t>Continuum_Removal</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -9280,24 +9280,24 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>-0.07715370692818549</v>
+        <v>-0.06632192505143117</v>
       </c>
       <c r="F211" t="n">
-        <v>1.152239602701967</v>
+        <v>0.6845914203170961</v>
       </c>
       <c r="G211" t="n">
-        <v>1.164233820286397</v>
+        <v>1.243255949211664</v>
       </c>
       <c r="H211" t="n">
-        <v>-0.07715370692818549</v>
+        <v>-0.06632192505143117</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 1, 'model__epsilon': 0.2, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J211" t="n">
-        <v>1.93484902381897</v>
+        <v>165.391393661499</v>
       </c>
     </row>
     <row r="212">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>SG_D1</t>
+          <t>Normalize</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -9322,24 +9322,24 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>-0.08060072737575807</v>
+        <v>-0.07715370692818549</v>
       </c>
       <c r="F212" t="n">
-        <v>0.5850845404533169</v>
+        <v>1.152239602701967</v>
       </c>
       <c r="G212" t="n">
-        <v>1.228552625524714</v>
+        <v>1.164233820286397</v>
       </c>
       <c r="H212" t="n">
-        <v>-0.08060072737575807</v>
+        <v>-0.07715370692818549</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J212" t="n">
-        <v>2.54093337059021</v>
+        <v>3.560302734375</v>
       </c>
     </row>
     <row r="213">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>OSC_1</t>
+          <t>OPLS1_SNV_SG_D1</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -9364,24 +9364,24 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>-0.09452942977912189</v>
+        <v>-0.07845099320806807</v>
       </c>
       <c r="F213" t="n">
-        <v>0.6080686027779706</v>
+        <v>0.9908656410181619</v>
       </c>
       <c r="G213" t="n">
-        <v>1.234335589593096</v>
+        <v>1.168805379845312</v>
       </c>
       <c r="H213" t="n">
-        <v>-0.09452942977912189</v>
+        <v>-0.07845099320806807</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>{'model__C': 1, 'model__epsilon': 0.5, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
+          <t>{'model__C': 100, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'linear'}</t>
         </is>
       </c>
       <c r="J213" t="n">
-        <v>2.084359169006348</v>
+        <v>8.142606496810913</v>
       </c>
     </row>
     <row r="214">
@@ -9392,38 +9392,38 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PCR</t>
+          <t>SVMR</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>SG_D2</t>
+          <t>OSC_1</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>-0.130998643660718</v>
+        <v>-0.09452942977912189</v>
       </c>
       <c r="F214" t="n">
-        <v>0.5835989800659611</v>
+        <v>0.6080686027779706</v>
       </c>
       <c r="G214" t="n">
-        <v>1.248244770145381</v>
+        <v>1.234335589593096</v>
       </c>
       <c r="H214" t="n">
-        <v>-0.130998643660718</v>
+        <v>-0.09452942977912189</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>{'model__pca__n_components': 15}</t>
+          <t>{'model__C': 1, 'model__epsilon': 0.5, 'model__gamma': 0.1, 'model__kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="J214" t="n">
-        <v>0.918461799621582</v>
+        <v>5.131686210632324</v>
       </c>
     </row>
     <row r="215">
@@ -9434,38 +9434,38 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>SVMR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>OPLS1_SNV_SG_D1</t>
+          <t>SG_D2</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>-0.1807162559736166</v>
+        <v>-0.1306739257549055</v>
       </c>
       <c r="F215" t="n">
-        <v>0.8869089641388228</v>
+        <v>0.5829325431584044</v>
       </c>
       <c r="G215" t="n">
-        <v>1.218902810877657</v>
+        <v>1.247900040053803</v>
       </c>
       <c r="H215" t="n">
-        <v>-0.1807162559736166</v>
+        <v>-0.1306739257549055</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>{'model__C': 10, 'model__epsilon': 0.1, 'model__gamma': 'scale', 'model__kernel': 'rbf'}</t>
+          <t>{'model__pca__n_components': 15}</t>
         </is>
       </c>
       <c r="J215" t="n">
-        <v>3.806965589523315</v>
+        <v>0.6097841262817383</v>
       </c>
     </row>
     <row r="216">
@@ -9490,16 +9490,16 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>-0.2025864437882823</v>
+        <v>-0.2025864437870658</v>
       </c>
       <c r="F216" t="n">
-        <v>1.547974868550945</v>
+        <v>1.547974868550859</v>
       </c>
       <c r="G216" t="n">
-        <v>1.166213620918864</v>
+        <v>1.166213620918583</v>
       </c>
       <c r="H216" t="n">
-        <v>-0.2025864437882823</v>
+        <v>-0.2025864437870658</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="J216" t="n">
-        <v>0.9906661510467529</v>
+        <v>0.5808396339416504</v>
       </c>
     </row>
     <row r="217">
@@ -9523,25 +9523,25 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>SNV_Detrend_SG_D1</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>dependente</t>
+          <t>independente</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>-0.226101068277397</v>
+        <v>-0.2261010682779628</v>
       </c>
       <c r="F217" t="n">
-        <v>1.673331808317524</v>
+        <v>1.67333180831706</v>
       </c>
       <c r="G217" t="n">
-        <v>1.167122673321425</v>
+        <v>1.167122673320717</v>
       </c>
       <c r="H217" t="n">
-        <v>-0.226101068277397</v>
+        <v>-0.2261010682779628</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>1.220409393310547</v>
+        <v>0.63037109375</v>
       </c>
     </row>
     <row r="218">
@@ -9565,25 +9565,25 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>SNV_Detrend_SG_D1</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>independente</t>
+          <t>dependente</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>-0.2261010682785217</v>
+        <v>-0.2261010682786549</v>
       </c>
       <c r="F218" t="n">
-        <v>1.673331808320158</v>
+        <v>1.673331808316705</v>
       </c>
       <c r="G218" t="n">
-        <v>1.1671226733211</v>
+        <v>1.167122673321531</v>
       </c>
       <c r="H218" t="n">
-        <v>-0.2261010682785217</v>
+        <v>-0.2261010682786549</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         </is>
       </c>
       <c r="J218" t="n">
-        <v>0.9492523670196533</v>
+        <v>0.5701284408569336</v>
       </c>
     </row>
     <row r="219">
@@ -9616,16 +9616,16 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>-0.2261107915587682</v>
+        <v>-0.226110791558919</v>
       </c>
       <c r="F219" t="n">
-        <v>1.673369307080873</v>
+        <v>1.673369307079132</v>
       </c>
       <c r="G219" t="n">
-        <v>1.167124956989449</v>
+        <v>1.167124956988011</v>
       </c>
       <c r="H219" t="n">
-        <v>-0.2261107915587682</v>
+        <v>-0.226110791558919</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         </is>
       </c>
       <c r="J219" t="n">
-        <v>1.016512870788574</v>
+        <v>0.8717086315155029</v>
       </c>
     </row>
     <row r="220">
@@ -9658,16 +9658,16 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>-0.2362797611998014</v>
+        <v>-0.2356677411001194</v>
       </c>
       <c r="F220" t="n">
-        <v>1.040818511490707</v>
+        <v>1.040728937625618</v>
       </c>
       <c r="G220" t="n">
-        <v>1.222360607872092</v>
+        <v>1.222199985982366</v>
       </c>
       <c r="H220" t="n">
-        <v>-0.2362797611998014</v>
+        <v>-0.2356677411001194</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         </is>
       </c>
       <c r="J220" t="n">
-        <v>0.8837473392486572</v>
+        <v>0.669191837310791</v>
       </c>
     </row>
     <row r="221">
@@ -9717,7 +9717,7 @@
         </is>
       </c>
       <c r="J221" t="n">
-        <v>0.785820484161377</v>
+        <v>0.5482733249664307</v>
       </c>
     </row>
     <row r="222">
@@ -9742,16 +9742,16 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>-0.2430808854481529</v>
+        <v>-0.2432722298305407</v>
       </c>
       <c r="F222" t="n">
-        <v>1.102841479835188</v>
+        <v>1.103705181835642</v>
       </c>
       <c r="G222" t="n">
-        <v>1.230990128953059</v>
+        <v>1.230933049893072</v>
       </c>
       <c r="H222" t="n">
-        <v>-0.2430808854481529</v>
+        <v>-0.2432722298305407</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         </is>
       </c>
       <c r="J222" t="n">
-        <v>1.029919862747192</v>
+        <v>0.6905243396759033</v>
       </c>
     </row>
     <row r="223">
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="J223" t="n">
-        <v>0.8253748416900635</v>
+        <v>0.6064765453338623</v>
       </c>
     </row>
     <row r="224">
@@ -9843,7 +9843,7 @@
         </is>
       </c>
       <c r="J224" t="n">
-        <v>0.6674385070800781</v>
+        <v>0.6264619827270508</v>
       </c>
     </row>
     <row r="225">
@@ -9885,7 +9885,7 @@
         </is>
       </c>
       <c r="J225" t="n">
-        <v>0.9452552795410156</v>
+        <v>0.6902260780334473</v>
       </c>
     </row>
     <row r="226">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>EMSC</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -9910,16 +9910,16 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>-0.3391493325691707</v>
+        <v>-0.3395986580344554</v>
       </c>
       <c r="F226" t="n">
-        <v>1.232969766144149</v>
+        <v>1.232979901210399</v>
       </c>
       <c r="G226" t="n">
-        <v>1.238794564394491</v>
+        <v>1.238773206741532</v>
       </c>
       <c r="H226" t="n">
-        <v>-0.3391493325691707</v>
+        <v>-0.3395986580344554</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         </is>
       </c>
       <c r="J226" t="n">
-        <v>1.070273160934448</v>
+        <v>0.6352808475494385</v>
       </c>
     </row>
     <row r="227">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>EMSC</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -9952,16 +9952,16 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>-0.3396811304289524</v>
+        <v>-0.3396222033074189</v>
       </c>
       <c r="F227" t="n">
-        <v>1.232836853832919</v>
+        <v>1.233540326759237</v>
       </c>
       <c r="G227" t="n">
-        <v>1.238405979663871</v>
+        <v>1.23876620674222</v>
       </c>
       <c r="H227" t="n">
-        <v>-0.3396811304289524</v>
+        <v>-0.3396222033074189</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="J227" t="n">
-        <v>1.07925009727478</v>
+        <v>0.679497241973877</v>
       </c>
     </row>
     <row r="228">
@@ -9994,16 +9994,16 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>-0.3974295755945944</v>
+        <v>-0.3971467622683587</v>
       </c>
       <c r="F228" t="n">
-        <v>1.352770404002468</v>
+        <v>1.353211878060289</v>
       </c>
       <c r="G228" t="n">
-        <v>1.264448999518628</v>
+        <v>1.264097477674671</v>
       </c>
       <c r="H228" t="n">
-        <v>-0.3974295755945944</v>
+        <v>-0.3971467622683587</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         </is>
       </c>
       <c r="J228" t="n">
-        <v>0.8387882709503174</v>
+        <v>0.6035351753234863</v>
       </c>
     </row>
     <row r="229">
@@ -10036,16 +10036,16 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>-0.4063507259483157</v>
+        <v>-0.4070919095734881</v>
       </c>
       <c r="F229" t="n">
-        <v>1.240197555399297</v>
+        <v>1.241589136340393</v>
       </c>
       <c r="G229" t="n">
-        <v>1.299292250456177</v>
+        <v>1.299188778150616</v>
       </c>
       <c r="H229" t="n">
-        <v>-0.4063507259483157</v>
+        <v>-0.4070919095734881</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="J229" t="n">
-        <v>0.9329736232757568</v>
+        <v>0.6134133338928223</v>
       </c>
     </row>
     <row r="230">
@@ -10078,16 +10078,16 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>-0.4236591408111093</v>
+        <v>-0.4235125154217838</v>
       </c>
       <c r="F230" t="n">
-        <v>1.338025942478819</v>
+        <v>1.338573378817281</v>
       </c>
       <c r="G230" t="n">
-        <v>1.292025390500712</v>
+        <v>1.291866942951363</v>
       </c>
       <c r="H230" t="n">
-        <v>-0.4236591408111093</v>
+        <v>-0.4235125154217838</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         </is>
       </c>
       <c r="J230" t="n">
-        <v>8.364047050476074</v>
+        <v>5.888067722320557</v>
       </c>
     </row>
     <row r="231">
@@ -10137,7 +10137,7 @@
         </is>
       </c>
       <c r="J231" t="n">
-        <v>0.7103402614593506</v>
+        <v>0.5509588718414307</v>
       </c>
     </row>
     <row r="232">
@@ -10179,7 +10179,7 @@
         </is>
       </c>
       <c r="J232" t="n">
-        <v>0.722973108291626</v>
+        <v>0.5958762168884277</v>
       </c>
     </row>
     <row r="233">
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="J233" t="n">
-        <v>0.9296908378601074</v>
+        <v>0.5573694705963135</v>
       </c>
     </row>
     <row r="234">
@@ -10263,7 +10263,7 @@
         </is>
       </c>
       <c r="J234" t="n">
-        <v>0.8865594863891602</v>
+        <v>0.7389633655548096</v>
       </c>
     </row>
     <row r="235">
@@ -10305,7 +10305,7 @@
         </is>
       </c>
       <c r="J235" t="n">
-        <v>0.820695161819458</v>
+        <v>0.6737060546875</v>
       </c>
     </row>
     <row r="236">
@@ -10347,7 +10347,7 @@
         </is>
       </c>
       <c r="J236" t="n">
-        <v>7.608492612838745</v>
+        <v>5.843706369400024</v>
       </c>
     </row>
     <row r="237">
@@ -10389,7 +10389,7 @@
         </is>
       </c>
       <c r="J237" t="n">
-        <v>0.8788888454437256</v>
+        <v>0.5611398220062256</v>
       </c>
     </row>
     <row r="238">
@@ -10431,7 +10431,7 @@
         </is>
       </c>
       <c r="J238" t="n">
-        <v>0.7252447605133057</v>
+        <v>0.7037646770477295</v>
       </c>
     </row>
     <row r="239">
@@ -10473,7 +10473,7 @@
         </is>
       </c>
       <c r="J239" t="n">
-        <v>0.941713809967041</v>
+        <v>0.8124732971191406</v>
       </c>
     </row>
     <row r="240">
@@ -10515,7 +10515,7 @@
         </is>
       </c>
       <c r="J240" t="n">
-        <v>0.755922794342041</v>
+        <v>0.5868234634399414</v>
       </c>
     </row>
     <row r="241">
@@ -10557,7 +10557,7 @@
         </is>
       </c>
       <c r="J241" t="n">
-        <v>0.9950363636016846</v>
+        <v>0.701265811920166</v>
       </c>
     </row>
   </sheetData>
